--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Oct_2026.xlsx
@@ -751,7 +751,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
@@ -1079,10 +1079,8 @@
           <t>Get Engineering Troop Pvt. Ltd.</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>9802344177</t>
-        </is>
+      <c r="O2" s="3" t="n">
+        <v>9802344177</v>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
@@ -1097,10 +1095,8 @@
       </c>
       <c r="S2" s="3" t="inlineStr"/>
       <c r="T2" s="3" t="inlineStr"/>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>9802344177</t>
-        </is>
+      <c r="U2" s="3" t="n">
+        <v>9802344177</v>
       </c>
       <c r="V2" s="3" t="inlineStr">
         <is>
@@ -1168,10 +1164,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN2" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN2" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO2" s="3" t="inlineStr">
         <is>
@@ -1182,7 +1176,7 @@
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr">
         <is>
-          <t>Case : REMOTE   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS2" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Oct_2026.xlsx
@@ -532,10 +532,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
@@ -572,7 +572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -628,7 +628,30 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -643,7 +666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -682,16 +705,29 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>1</v>
+      <c r="B4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -705,7 +741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX2"/>
+  <dimension ref="A1:AX3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -739,7 +775,7 @@
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="12" customWidth="1" min="32" max="32"/>
+    <col width="24" customWidth="1" min="32" max="32"/>
     <col width="27" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -751,7 +787,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
@@ -1210,6 +1246,222 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 9:36 AM</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>TKT1380806</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>Aayush shrestha</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>Aayush shrestha</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>9843468465</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 09:36:28 AM</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>9843468465</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 09:07:13 PM</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 09:36:28 AM</t>
+        </is>
+      </c>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="inlineStr">
+        <is>
+          <t>27.67349</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC3" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD3" s="3" t="inlineStr"/>
+      <c r="AE3" s="3" t="inlineStr">
+        <is>
+          <t>Bhaktapur, ghatthaghar near by nepal telecom, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF3" s="3" t="inlineStr">
+        <is>
+          <t>aayushsth77@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG3" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH3" s="3" t="inlineStr"/>
+      <c r="AI3" s="3" t="inlineStr">
+        <is>
+          <t>10:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM3" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN3" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>L51-6</t>
+        </is>
+      </c>
+      <c r="AP3" s="3" t="inlineStr">
+        <is>
+          <t>85.37342</t>
+        </is>
+      </c>
+      <c r="AQ3" s="3" t="inlineStr"/>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>1d 12h 29m</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX3" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Oct_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -528,14 +528,14 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Shashikant Chaudhary</t>
+          <t>Sanjeev Giri</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -544,18 +544,36 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="B4" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -628,7 +646,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -639,10 +657,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -651,7 +669,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -666,12 +684,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -682,10 +701,15 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -694,26 +718,32 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>IPTV Remote damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="6" t="n">
+      <c r="C2" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="D2" s="6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV Remote damage Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="6" t="n">
+      <c r="D3" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -724,10 +754,13 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>2</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -741,7 +774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX3"/>
+  <dimension ref="A1:AX4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -781,7 +814,7 @@
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="14" customWidth="1" min="38" max="38"/>
+    <col width="15" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
@@ -1313,10 +1346,8 @@
           <t>Aayush shrestha</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>9843468465</t>
-        </is>
+      <c r="O3" s="3" t="n">
+        <v>9843468465</v>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
@@ -1331,10 +1362,8 @@
       </c>
       <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="3" t="inlineStr"/>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>9843468465</t>
-        </is>
+      <c r="U3" s="3" t="n">
+        <v>9843468465</v>
       </c>
       <c r="V3" s="3" t="inlineStr">
         <is>
@@ -1351,10 +1380,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y3" s="3" t="inlineStr">
-        <is>
-          <t>27.67349</t>
-        </is>
+      <c r="Y3" s="3" t="n">
+        <v>27.67349</v>
       </c>
       <c r="Z3" s="3" t="inlineStr">
         <is>
@@ -1410,55 +1437,259 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN3" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO3" s="3" t="inlineStr">
         <is>
           <t>L51-6</t>
         </is>
       </c>
-      <c r="AP3" s="3" t="inlineStr">
-        <is>
-          <t>85.37342</t>
-        </is>
+      <c r="AP3" s="3" t="n">
+        <v>85.37342</v>
       </c>
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>1d 12h 29m</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS3" s="3" t="inlineStr">
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX3" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 9:54 AM</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>TKT1381026</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Sujal Pokherel</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Follow Up</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Sujal Pokherel</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>9861607603</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 09:54:03 AM</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>9861607603</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 10:02:51 AM</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 09:54:03 AM</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr"/>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr"/>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>Near Panchpokhari Model Sec School P9GM+RQH, Gokarneshwor 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr">
+        <is>
+          <t>n8e5s8n5@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG4" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr">
+        <is>
+          <t>09:58 hour</t>
+        </is>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>Kusum Gurung</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>L30-5</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr"/>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT3" s="3" t="inlineStr">
-        <is>
-          <t>1d 12h 29m</t>
-        </is>
-      </c>
-      <c r="AU3" s="3" t="inlineStr">
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>23h 51m</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV3" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW3" s="3" t="inlineStr">
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW4" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX3" s="3" t="inlineStr">
-        <is>
-          <t>Shashikant Chaudhary</t>
+      <c r="AX4" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Oct_2026.xlsx
@@ -820,7 +820,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
@@ -1552,10 +1552,8 @@
           <t>Sujal Pokherel</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>9861607603</t>
-        </is>
+      <c r="O4" s="3" t="n">
+        <v>9861607603</v>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
@@ -1570,10 +1568,8 @@
       </c>
       <c r="S4" s="3" t="inlineStr"/>
       <c r="T4" s="3" t="inlineStr"/>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t>9861607603</t>
-        </is>
+      <c r="U4" s="3" t="n">
+        <v>9861607603</v>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
@@ -1645,10 +1641,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN4" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
@@ -1659,7 +1653,7 @@
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Oct_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -528,7 +528,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Sanjeev Giri</t>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
@@ -546,36 +546,72 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Shashikant Chaudhary</t>
+          <t>Sanjeev Giri</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>100.0%</t>
+      <c r="B6" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>81.8%</t>
         </is>
       </c>
     </row>
@@ -634,19 +670,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>63.6%</t>
         </is>
       </c>
     </row>
@@ -657,19 +693,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>36.4%</t>
         </is>
       </c>
     </row>
@@ -684,13 +720,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="39" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -701,15 +739,25 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -725,42 +773,148 @@
         <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="6" t="n">
-        <v>2</v>
+      <c r="E2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="6" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>IPTV Remote damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="E3" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="F3" s="6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>IPTV STB Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Remote damage Issue</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>ONT and Setup Box Recovery</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Query For Secondary Router /Repeater</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B8" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D4" s="4" t="n">
-        <v>3</v>
+      <c r="F8" s="4" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -774,18 +928,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX4"/>
+  <dimension ref="A1:AX12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="34" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
@@ -797,33 +951,33 @@
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
     <col width="37" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
-    <col width="15" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
+    <col width="17" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="24" customWidth="1" min="32" max="32"/>
-    <col width="27" customWidth="1" min="33" max="33"/>
+    <col width="28" customWidth="1" min="32" max="32"/>
+    <col width="39" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="15" customWidth="1" min="38" max="38"/>
+    <col width="20" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
-    <col width="24" customWidth="1" min="47" max="47"/>
+    <col width="32" customWidth="1" min="47" max="47"/>
     <col width="45" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
     <col width="23" customWidth="1" min="50" max="50"/>
@@ -1687,6 +1841,1698 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 10:47 AM</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 router upgrade</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>TKT1377993</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Yubraj Bhattarai</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Yubraj Bhattarai</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>9851110377</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 10:47:38 AM</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>9851110377</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 12:14:38 PM</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 10:47:38 AM</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t>27.73578</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="inlineStr"/>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>near Fishery Development Directorate  Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr">
+        <is>
+          <t>ewarajbhattarai@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG5" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH5" s="3" t="inlineStr"/>
+      <c r="AI5" s="3" t="inlineStr"/>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>Mamata Bhujel</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>1,10</t>
+        </is>
+      </c>
+      <c r="AP5" s="3" t="inlineStr">
+        <is>
+          <t>85.30316</t>
+        </is>
+      </c>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>3d 22h 33m</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX5" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 10:42 AM</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Case : internet not working  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>internet not working</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>TKT1377795</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Rohit Oli</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>Rohit Oli</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>9857890358</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 10:42:32 AM</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>9857890358</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 09:57:04 AM</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 10:42:32 AM</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr">
+        <is>
+          <t>27.75313</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr"/>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>Goldhunbga near Tarkeshwar Ward no. 5 office, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr">
+        <is>
+          <t>rohitoli143@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG6" s="3" t="inlineStr">
+        <is>
+          <t>Query For Secondary Router /Repeater</t>
+        </is>
+      </c>
+      <c r="AH6" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI6" s="3" t="inlineStr">
+        <is>
+          <t>06:42 hour</t>
+        </is>
+      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>L62-5</t>
+        </is>
+      </c>
+      <c r="AP6" s="3" t="inlineStr">
+        <is>
+          <t>85.284</t>
+        </is>
+      </c>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>Case : internet not working  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>4d 45m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>Case : internet not working  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX6" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 10:38 AM</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>TKT1380909</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Bibek shrestha</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Bibek shrestha</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>9819236730</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 10:38:20 AM</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>LTP9819236730</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 08:08:50 AM</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 10:38:20 AM</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr"/>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr"/>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>near by N.S Parlour and Training Center - Beauty salon Lalitpur 44700, Lalitpur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr">
+        <is>
+          <t>bibekcrestha05@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr"/>
+      <c r="AI7" s="3" t="inlineStr">
+        <is>
+          <t>10:38 hour</t>
+        </is>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>2,13</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr"/>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 29m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX7" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 11:01 AM</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Case : router collection  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>router collection</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>TKT1381055</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Pedal budhathoki</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Pedal budhathoki</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>9869643717</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>Device Recovery</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 10:29:41 AM</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>KLK9869643717</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 10:29:41 AM</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 11:01:11 AM</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr"/>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>Device Recovery</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr"/>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>Balaju bhatbhatine, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr">
+        <is>
+          <t>Pes@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG8" s="3" t="inlineStr">
+        <is>
+          <t>ONT and Setup Box Recovery</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="inlineStr"/>
+      <c r="AI8" s="3" t="inlineStr"/>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr">
+        <is>
+          <t>Joshna Shrestha</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>CDB553</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr"/>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>Case : router collection  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>1d 31m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>1d 31m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
+          <t>Case : router collection  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX8" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 10:52 AM</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Case : blank display  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>blank display</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379324</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Bhupendra oli</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Bhupendra oli</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>9852027449</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 04:15:42 PM</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>9852027449</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 03:40:19 PM</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 10:52:17 AM</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr"/>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr"/>
+      <c r="AE9" s="3" t="inlineStr">
+        <is>
+          <t>Janajagriti Gyan Rashmi Secondary School - Government school P7JV+3QC kharibot station, Banasthhali</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="inlineStr">
+        <is>
+          <t>olibhupendra233@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG9" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH9" s="3" t="inlineStr"/>
+      <c r="AI9" s="3" t="inlineStr">
+        <is>
+          <t>01:11 hour</t>
+        </is>
+      </c>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr">
+        <is>
+          <t>Keshab Magar</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>CDB287</t>
+        </is>
+      </c>
+      <c r="AP9" s="3" t="inlineStr"/>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>Case : blank display  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>2d 18h 36m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>2d 19h 11m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
+          <t>Case : blank display  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX9" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 10:51 AM</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Case : blank display  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>blank display</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379324</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Bhupendra oli</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Bhupendra oli</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>9852027449</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 04:15:42 PM</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>9852027449</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 03:40:19 PM</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 10:52:17 AM</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr"/>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr"/>
+      <c r="AE10" s="3" t="inlineStr">
+        <is>
+          <t>Janajagriti Gyan Rashmi Secondary School - Government school P7JV+3QC kharibot station, Banasthhali</t>
+        </is>
+      </c>
+      <c r="AF10" s="3" t="inlineStr">
+        <is>
+          <t>olibhupendra233@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG10" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr">
+        <is>
+          <t>01:11 hour</t>
+        </is>
+      </c>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr">
+        <is>
+          <t>Keshab Magar</t>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>CDB287</t>
+        </is>
+      </c>
+      <c r="AP10" s="3" t="inlineStr"/>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>Case : blank display  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>2d 18h 36m</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>2d 19h 11m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
+          <t>Case : blank display  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX10" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 10:58 AM</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>no light blinking</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>TKT1380263</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Shrestha</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Shrestha</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>9849304154</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 10:58:23 AM</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>9849304154</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 01:25:20 PM</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 10:58:23 AM</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr">
+        <is>
+          <t>27.68994</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA11" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC11" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="inlineStr"/>
+      <c r="AE11" s="3" t="inlineStr">
+        <is>
+          <t>Near Motherland Hospital Pvt. Ltd, Thapagaon, Pepsicola Road, Pepsicola, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF11" s="3" t="inlineStr">
+        <is>
+          <t>surya204721@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG11" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="3" t="inlineStr">
+        <is>
+          <t>17:33 hour</t>
+        </is>
+      </c>
+      <c r="AJ11" s="3" t="inlineStr"/>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr">
+        <is>
+          <t>Pramila Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM11" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN11" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO11" s="3" t="inlineStr">
+        <is>
+          <t>L17-7</t>
+        </is>
+      </c>
+      <c r="AP11" s="3" t="inlineStr">
+        <is>
+          <t>85.3633</t>
+        </is>
+      </c>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>1d 21h 33m</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX11" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 10:31 AM</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Case : SETUP BOX ISSUE   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>SETUP BOX ISSUE</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>TKT1380277</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Amrisha Karanjit</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Amrisha Karanjit</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>9841285247</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 10:31:13 AM</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>9841285247</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 01:34:51 PM</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 10:31:13 AM</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr">
+        <is>
+          <t>27.683009</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC12" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr"/>
+      <c r="AE12" s="3" t="inlineStr">
+        <is>
+          <t>Madhyapur Thimi , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF12" s="3" t="inlineStr">
+        <is>
+          <t>amrishakaranjit@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG12" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH12" s="3" t="inlineStr"/>
+      <c r="AI12" s="3" t="inlineStr">
+        <is>
+          <t>16:57 hour</t>
+        </is>
+      </c>
+      <c r="AJ12" s="3" t="inlineStr"/>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr">
+        <is>
+          <t>Sanam Sadar</t>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr">
+        <is>
+          <t>85.386192</t>
+        </is>
+      </c>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>Case : SETUP BOX ISSUE   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>1d 20h 56m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
+          <t>Case : SETUP BOX ISSUE   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX12" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Oct_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -528,90 +528,108 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Rajesh Maharjan</t>
+          <t>Chandramani Tharu</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Sanjeev Giri</t>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Shashikant Chaudhary</t>
+          <t>Sanjeev Giri</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Sunil Chaudhary</t>
+          <t>Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="C6" s="4" t="n">
+      <c r="B7" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="C7" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>81.8%</t>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>64.3%</t>
         </is>
       </c>
     </row>
@@ -682,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -705,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>28.6%</t>
         </is>
       </c>
     </row>
@@ -720,7 +738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -810,7 +828,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB Adaptor damage Issue</t>
+          <t>IPTV Remote damage Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -832,7 +850,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>IPTV Remote damage Issue</t>
+          <t>IPTV STB Adaptor damage Issue</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -876,45 +894,67 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Query For Secondary Router /Repeater</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Query For Secondary Router /Repeater</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B9" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C9" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D9" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="E8" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>10</v>
+      <c r="E9" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -928,7 +968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX12"/>
+  <dimension ref="A1:AX15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -974,7 +1014,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -1908,10 +1948,8 @@
           <t>Yubraj Bhattarai</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>9851110377</t>
-        </is>
+      <c r="O5" s="3" t="n">
+        <v>9851110377</v>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
@@ -1946,10 +1984,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y5" s="3" t="inlineStr">
-        <is>
-          <t>27.73578</t>
-        </is>
+      <c r="Y5" s="3" t="n">
+        <v>27.73578</v>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
@@ -2001,25 +2037,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN5" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN5" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO5" s="3" t="inlineStr">
         <is>
           <t>1,10</t>
         </is>
       </c>
-      <c r="AP5" s="3" t="inlineStr">
-        <is>
-          <t>85.30316</t>
-        </is>
+      <c r="AP5" s="3" t="n">
+        <v>85.30316000000001</v>
       </c>
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 router upgrade   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS5" s="3" t="inlineStr">
@@ -2120,10 +2152,8 @@
           <t>Rohit Oli</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>9857890358</t>
-        </is>
+      <c r="O6" s="3" t="n">
+        <v>9857890358</v>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
@@ -2158,10 +2188,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y6" s="3" t="inlineStr">
-        <is>
-          <t>27.75313</t>
-        </is>
+      <c r="Y6" s="3" t="n">
+        <v>27.75313</v>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
@@ -2199,10 +2227,8 @@
           <t>Query For Secondary Router /Repeater</t>
         </is>
       </c>
-      <c r="AH6" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH6" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI6" s="3" t="inlineStr">
         <is>
@@ -2221,25 +2247,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN6" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN6" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO6" s="3" t="inlineStr">
         <is>
           <t>L62-5</t>
         </is>
       </c>
-      <c r="AP6" s="3" t="inlineStr">
-        <is>
-          <t>85.284</t>
-        </is>
+      <c r="AP6" s="3" t="n">
+        <v>85.28400000000001</v>
       </c>
       <c r="AQ6" s="3" t="inlineStr"/>
       <c r="AR6" s="3" t="inlineStr">
         <is>
-          <t>Case : internet not working  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS6" s="3" t="inlineStr">
@@ -2340,10 +2362,8 @@
           <t>Bibek shrestha</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>9819236730</t>
-        </is>
+      <c r="O7" s="3" t="n">
+        <v>9819236730</v>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
@@ -2433,10 +2453,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN7" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN7" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
@@ -2447,7 +2465,7 @@
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS7" s="3" t="inlineStr">
@@ -2538,20 +2556,14 @@
           <t>On Hold</t>
         </is>
       </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M8" s="3" t="inlineStr"/>
       <c r="N8" s="3" t="inlineStr">
         <is>
           <t>Pedal budhathoki</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>9869643717</t>
-        </is>
+      <c r="O8" s="3" t="n">
+        <v>9869643717</v>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
@@ -2637,10 +2649,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN8" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN8" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
@@ -2651,7 +2661,7 @@
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr">
         <is>
-          <t>Case : router collection  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS8" s="3" t="inlineStr">
@@ -2752,10 +2762,8 @@
           <t>Bhupendra oli</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>9852027449</t>
-        </is>
+      <c r="O9" s="3" t="n">
+        <v>9852027449</v>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
@@ -2845,10 +2853,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN9" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
@@ -2859,7 +2865,7 @@
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr">
         <is>
-          <t>Case : blank display  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS9" s="3" t="inlineStr">
@@ -2960,10 +2966,8 @@
           <t>Bhupendra oli</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>9852027449</t>
-        </is>
+      <c r="O10" s="3" t="n">
+        <v>9852027449</v>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
@@ -3053,10 +3057,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN10" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN10" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
@@ -3067,7 +3069,7 @@
       <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>Case : blank display  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">
@@ -3168,10 +3170,8 @@
           <t>Sanjeev Shrestha</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>9849304154</t>
-        </is>
+      <c r="O11" s="3" t="n">
+        <v>9849304154</v>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
@@ -3206,10 +3206,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t>27.68994</t>
-        </is>
+      <c r="Y11" s="3" t="n">
+        <v>27.68994</v>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
@@ -3265,25 +3263,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN11" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN11" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
           <t>L17-7</t>
         </is>
       </c>
-      <c r="AP11" s="3" t="inlineStr">
-        <is>
-          <t>85.3633</t>
-        </is>
+      <c r="AP11" s="3" t="n">
+        <v>85.3633</v>
       </c>
       <c r="AQ11" s="3" t="inlineStr"/>
       <c r="AR11" s="3" t="inlineStr">
         <is>
-          <t>Case : no light blinking  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS11" s="3" t="inlineStr">
@@ -3384,10 +3378,8 @@
           <t>Amrisha Karanjit</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>9841285247</t>
-        </is>
+      <c r="O12" s="3" t="n">
+        <v>9841285247</v>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
@@ -3422,10 +3414,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y12" s="3" t="inlineStr">
-        <is>
-          <t>27.683009</t>
-        </is>
+      <c r="Y12" s="3" t="n">
+        <v>27.683009</v>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
@@ -3481,47 +3471,43 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN12" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
           <t>L9-1</t>
         </is>
       </c>
-      <c r="AP12" s="3" t="inlineStr">
-        <is>
-          <t>85.386192</t>
-        </is>
+      <c r="AP12" s="3" t="n">
+        <v>85.38619199999999</v>
       </c>
       <c r="AQ12" s="3" t="inlineStr"/>
       <c r="AR12" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>1d 20h 56m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
           <t>Case : SETUP BOX ISSUE   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS12" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT12" s="3" t="inlineStr">
-        <is>
-          <t>1d 20h 56m</t>
-        </is>
-      </c>
-      <c r="AU12" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV12" s="3" t="inlineStr">
-        <is>
-          <t>Case : SETUP BOX ISSUE   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="AW12" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
@@ -3530,6 +3516,330 @@
       <c r="AX12" s="3" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 11:10 AM</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Case : SLOW ISSUE  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr"/>
+      <c r="J13" s="3" t="inlineStr"/>
+      <c r="K13" s="3" t="inlineStr"/>
+      <c r="L13" s="3" t="inlineStr"/>
+      <c r="M13" s="3" t="inlineStr"/>
+      <c r="N13" s="3" t="inlineStr"/>
+      <c r="O13" s="3" t="inlineStr"/>
+      <c r="P13" s="3" t="inlineStr"/>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr"/>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr"/>
+      <c r="U13" s="3" t="inlineStr"/>
+      <c r="V13" s="3" t="inlineStr"/>
+      <c r="W13" s="3" t="inlineStr"/>
+      <c r="X13" s="3" t="inlineStr"/>
+      <c r="Y13" s="3" t="inlineStr"/>
+      <c r="Z13" s="3" t="inlineStr"/>
+      <c r="AA13" s="3" t="inlineStr"/>
+      <c r="AB13" s="3" t="inlineStr"/>
+      <c r="AC13" s="3" t="inlineStr"/>
+      <c r="AD13" s="3" t="inlineStr"/>
+      <c r="AE13" s="3" t="inlineStr"/>
+      <c r="AF13" s="3" t="inlineStr"/>
+      <c r="AG13" s="3" t="inlineStr"/>
+      <c r="AH13" s="3" t="inlineStr"/>
+      <c r="AI13" s="3" t="inlineStr"/>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="3" t="inlineStr"/>
+      <c r="AL13" s="3" t="inlineStr"/>
+      <c r="AM13" s="3" t="inlineStr"/>
+      <c r="AN13" s="3" t="inlineStr"/>
+      <c r="AO13" s="3" t="inlineStr"/>
+      <c r="AP13" s="3" t="inlineStr"/>
+      <c r="AQ13" s="3" t="inlineStr"/>
+      <c r="AR13" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
+          <t>Case : SLOW ISSUE  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX13" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 10:30 AM</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr"/>
+      <c r="J14" s="3" t="inlineStr"/>
+      <c r="K14" s="3" t="inlineStr"/>
+      <c r="L14" s="3" t="inlineStr"/>
+      <c r="M14" s="3" t="inlineStr"/>
+      <c r="N14" s="3" t="inlineStr"/>
+      <c r="O14" s="3" t="inlineStr"/>
+      <c r="P14" s="3" t="inlineStr"/>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr"/>
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="3" t="inlineStr"/>
+      <c r="V14" s="3" t="inlineStr"/>
+      <c r="W14" s="3" t="inlineStr"/>
+      <c r="X14" s="3" t="inlineStr"/>
+      <c r="Y14" s="3" t="inlineStr"/>
+      <c r="Z14" s="3" t="inlineStr"/>
+      <c r="AA14" s="3" t="inlineStr"/>
+      <c r="AB14" s="3" t="inlineStr"/>
+      <c r="AC14" s="3" t="inlineStr"/>
+      <c r="AD14" s="3" t="inlineStr"/>
+      <c r="AE14" s="3" t="inlineStr"/>
+      <c r="AF14" s="3" t="inlineStr"/>
+      <c r="AG14" s="3" t="inlineStr"/>
+      <c r="AH14" s="3" t="inlineStr"/>
+      <c r="AI14" s="3" t="inlineStr"/>
+      <c r="AJ14" s="3" t="inlineStr"/>
+      <c r="AK14" s="3" t="inlineStr"/>
+      <c r="AL14" s="3" t="inlineStr"/>
+      <c r="AM14" s="3" t="inlineStr"/>
+      <c r="AN14" s="3" t="inlineStr"/>
+      <c r="AO14" s="3" t="inlineStr"/>
+      <c r="AP14" s="3" t="inlineStr"/>
+      <c r="AQ14" s="3" t="inlineStr"/>
+      <c r="AR14" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV14" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX14" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 11:07 AM</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr"/>
+      <c r="J15" s="3" t="inlineStr"/>
+      <c r="K15" s="3" t="inlineStr"/>
+      <c r="L15" s="3" t="inlineStr"/>
+      <c r="M15" s="3" t="inlineStr"/>
+      <c r="N15" s="3" t="inlineStr"/>
+      <c r="O15" s="3" t="inlineStr"/>
+      <c r="P15" s="3" t="inlineStr"/>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr"/>
+      <c r="S15" s="3" t="inlineStr"/>
+      <c r="T15" s="3" t="inlineStr"/>
+      <c r="U15" s="3" t="inlineStr"/>
+      <c r="V15" s="3" t="inlineStr"/>
+      <c r="W15" s="3" t="inlineStr"/>
+      <c r="X15" s="3" t="inlineStr"/>
+      <c r="Y15" s="3" t="inlineStr"/>
+      <c r="Z15" s="3" t="inlineStr"/>
+      <c r="AA15" s="3" t="inlineStr"/>
+      <c r="AB15" s="3" t="inlineStr"/>
+      <c r="AC15" s="3" t="inlineStr"/>
+      <c r="AD15" s="3" t="inlineStr"/>
+      <c r="AE15" s="3" t="inlineStr"/>
+      <c r="AF15" s="3" t="inlineStr"/>
+      <c r="AG15" s="3" t="inlineStr"/>
+      <c r="AH15" s="3" t="inlineStr"/>
+      <c r="AI15" s="3" t="inlineStr"/>
+      <c r="AJ15" s="3" t="inlineStr"/>
+      <c r="AK15" s="3" t="inlineStr"/>
+      <c r="AL15" s="3" t="inlineStr"/>
+      <c r="AM15" s="3" t="inlineStr"/>
+      <c r="AN15" s="3" t="inlineStr"/>
+      <c r="AO15" s="3" t="inlineStr"/>
+      <c r="AP15" s="3" t="inlineStr"/>
+      <c r="AQ15" s="3" t="inlineStr"/>
+      <c r="AR15" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV15" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW15" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX15" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Oct_2026.xlsx
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>4</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>9</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>46.7%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>26.7%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX15"/>
+  <dimension ref="A1:AX16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -3843,6 +3843,114 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 11:30 AM</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr"/>
+      <c r="J16" s="3" t="inlineStr"/>
+      <c r="K16" s="3" t="inlineStr"/>
+      <c r="L16" s="3" t="inlineStr"/>
+      <c r="M16" s="3" t="inlineStr"/>
+      <c r="N16" s="3" t="inlineStr"/>
+      <c r="O16" s="3" t="inlineStr"/>
+      <c r="P16" s="3" t="inlineStr"/>
+      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="inlineStr"/>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="3" t="inlineStr"/>
+      <c r="U16" s="3" t="inlineStr"/>
+      <c r="V16" s="3" t="inlineStr"/>
+      <c r="W16" s="3" t="inlineStr"/>
+      <c r="X16" s="3" t="inlineStr"/>
+      <c r="Y16" s="3" t="inlineStr"/>
+      <c r="Z16" s="3" t="inlineStr"/>
+      <c r="AA16" s="3" t="inlineStr"/>
+      <c r="AB16" s="3" t="inlineStr"/>
+      <c r="AC16" s="3" t="inlineStr"/>
+      <c r="AD16" s="3" t="inlineStr"/>
+      <c r="AE16" s="3" t="inlineStr"/>
+      <c r="AF16" s="3" t="inlineStr"/>
+      <c r="AG16" s="3" t="inlineStr"/>
+      <c r="AH16" s="3" t="inlineStr"/>
+      <c r="AI16" s="3" t="inlineStr"/>
+      <c r="AJ16" s="3" t="inlineStr"/>
+      <c r="AK16" s="3" t="inlineStr"/>
+      <c r="AL16" s="3" t="inlineStr"/>
+      <c r="AM16" s="3" t="inlineStr"/>
+      <c r="AN16" s="3" t="inlineStr"/>
+      <c r="AO16" s="3" t="inlineStr"/>
+      <c r="AP16" s="3" t="inlineStr"/>
+      <c r="AQ16" s="3" t="inlineStr"/>
+      <c r="AR16" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU16" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV16" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW16" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX16" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Oct_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>68.4%</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>36.8%</t>
         </is>
       </c>
     </row>
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>87.5%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>42.1%</t>
         </is>
       </c>
     </row>
@@ -788,19 +788,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -942,19 +942,19 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>4</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -968,7 +968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX16"/>
+  <dimension ref="A1:AX20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -991,7 +991,7 @@
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
     <col width="37" customWidth="1" min="20" max="20"/>
-    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="27" customWidth="1" min="21" max="21"/>
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
@@ -1002,7 +1002,7 @@
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="28" customWidth="1" min="32" max="32"/>
+    <col width="29" customWidth="1" min="32" max="32"/>
     <col width="39" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -1014,7 +1014,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -3951,6 +3951,866 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 11:34 AM</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>TKT1380100</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Pradip Poudel</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>Pradip Poudel</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>9849120697</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr"/>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 11:33:59 AM</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr"/>
+      <c r="T17" s="3" t="inlineStr"/>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>9849120697</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 11:29:16 AM</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 11:33:59 AM</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y17" s="3" t="inlineStr">
+        <is>
+          <t>27.6655</t>
+        </is>
+      </c>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA17" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC17" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD17" s="3" t="inlineStr"/>
+      <c r="AE17" s="3" t="inlineStr">
+        <is>
+          <t>Near Budhi Bikash Football Ground, Lagankhel, Lalitpur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF17" s="3" t="inlineStr">
+        <is>
+          <t>grng_pradip@yahoo.com</t>
+        </is>
+      </c>
+      <c r="AG17" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH17" s="3" t="inlineStr"/>
+      <c r="AI17" s="3" t="inlineStr">
+        <is>
+          <t>20:05 hour</t>
+        </is>
+      </c>
+      <c r="AJ17" s="3" t="inlineStr"/>
+      <c r="AK17" s="3" t="inlineStr"/>
+      <c r="AL17" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM17" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN17" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO17" s="3" t="inlineStr">
+        <is>
+          <t>CDB927</t>
+        </is>
+      </c>
+      <c r="AP17" s="3" t="inlineStr">
+        <is>
+          <t>85.32093</t>
+        </is>
+      </c>
+      <c r="AQ17" s="3" t="inlineStr"/>
+      <c r="AR17" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>2d 4m</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW17" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX17" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 11:44 AM</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Router Upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>WIFI6 Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379150</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>Hotel Parbat Samjhana</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>Hotel Parbat Samjhana</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>9851322044</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr"/>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 11:44:58 AM</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr"/>
+      <c r="T18" s="3" t="inlineStr"/>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t>9808547970</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 01:14:24 PM</t>
+        </is>
+      </c>
+      <c r="W18" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 11:44:58 AM</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y18" s="3" t="inlineStr">
+        <is>
+          <t>27.73037</t>
+        </is>
+      </c>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA18" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB18" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC18" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD18" s="3" t="inlineStr"/>
+      <c r="AE18" s="3" t="inlineStr">
+        <is>
+          <t>Gongabu, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF18" s="3" t="inlineStr">
+        <is>
+          <t>shresthabipin227@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG18" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH18" s="3" t="inlineStr"/>
+      <c r="AI18" s="3" t="inlineStr">
+        <is>
+          <t>04:30 hour</t>
+        </is>
+      </c>
+      <c r="AJ18" s="3" t="inlineStr"/>
+      <c r="AK18" s="3" t="inlineStr"/>
+      <c r="AL18" s="3" t="inlineStr">
+        <is>
+          <t>Aashna Pulami</t>
+        </is>
+      </c>
+      <c r="AM18" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN18" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO18" s="3" t="inlineStr">
+        <is>
+          <t>L33-2</t>
+        </is>
+      </c>
+      <c r="AP18" s="3" t="inlineStr">
+        <is>
+          <t>85.31158</t>
+        </is>
+      </c>
+      <c r="AQ18" s="3" t="inlineStr"/>
+      <c r="AR18" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Router Upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>2d 22h 30m</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV18" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Router Upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW18" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX18" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 11:36 AM</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6 Router Upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>wifi6 Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379142</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>Hotel Parbat Samjhana</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>Hotel Parbat Samjhana</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>9851322044</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 11:36:37 AM</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr"/>
+      <c r="T19" s="3" t="inlineStr"/>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>hotelparbatsamjhana_fttx</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 01:08:44 PM</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 11:36:37 AM</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y19" s="3" t="inlineStr">
+        <is>
+          <t>27.73029</t>
+        </is>
+      </c>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA19" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB19" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC19" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD19" s="3" t="inlineStr"/>
+      <c r="AE19" s="3" t="inlineStr">
+        <is>
+          <t>Nepal Telecom Mitranagar Marg, Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF19" s="3" t="inlineStr">
+        <is>
+          <t>shresthabipin227@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG19" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH19" s="3" t="inlineStr"/>
+      <c r="AI19" s="3" t="inlineStr">
+        <is>
+          <t>04:28 hour</t>
+        </is>
+      </c>
+      <c r="AJ19" s="3" t="inlineStr"/>
+      <c r="AK19" s="3" t="inlineStr"/>
+      <c r="AL19" s="3" t="inlineStr">
+        <is>
+          <t>Aashna Pulami</t>
+        </is>
+      </c>
+      <c r="AM19" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN19" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO19" s="3" t="inlineStr">
+        <is>
+          <t>L33-2</t>
+        </is>
+      </c>
+      <c r="AP19" s="3" t="inlineStr">
+        <is>
+          <t>85.31154</t>
+        </is>
+      </c>
+      <c r="AQ19" s="3" t="inlineStr"/>
+      <c r="AR19" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6 Router Upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>2d 22h 27m</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6 Router Upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW19" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX19" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 11:43 AM</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>TKT1381095</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>Rajiv Pandey</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>Rajiv Pandey</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>9745326628</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q20" s="3" t="inlineStr"/>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 10:53:30 AM</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="inlineStr"/>
+      <c r="T20" s="3" t="inlineStr"/>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t>9745326658</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 10:53:30 AM</t>
+        </is>
+      </c>
+      <c r="W20" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 11:43:27 AM</t>
+        </is>
+      </c>
+      <c r="X20" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y20" s="3" t="inlineStr">
+        <is>
+          <t>27.67518</t>
+        </is>
+      </c>
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA20" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB20" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC20" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD20" s="3" t="inlineStr"/>
+      <c r="AE20" s="3" t="inlineStr">
+        <is>
+          <t>Near Bijeshwori Gyan Mandir Sainik Mahavidyalaya, Sainik Awas Marg, Kathmandu, Bagmati, Central, Nep</t>
+        </is>
+      </c>
+      <c r="AF20" s="3" t="inlineStr"/>
+      <c r="AG20" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH20" s="3" t="inlineStr"/>
+      <c r="AI20" s="3" t="inlineStr">
+        <is>
+          <t>10:50 hour</t>
+        </is>
+      </c>
+      <c r="AJ20" s="3" t="inlineStr"/>
+      <c r="AK20" s="3" t="inlineStr"/>
+      <c r="AL20" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM20" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN20" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO20" s="3" t="inlineStr">
+        <is>
+          <t>3,14</t>
+        </is>
+      </c>
+      <c r="AP20" s="3" t="inlineStr">
+        <is>
+          <t>85.378529</t>
+        </is>
+      </c>
+      <c r="AQ20" s="3" t="inlineStr"/>
+      <c r="AR20" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
+        <is>
+          <t>1d 49m</t>
+        </is>
+      </c>
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>1d 49m</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV20" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW20" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX20" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Oct_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>70.0%</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>35.0%</t>
         </is>
       </c>
     </row>
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>7</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>45.0%</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>4</v>
@@ -800,7 +800,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>5</v>
@@ -954,7 +954,7 @@
         <v>4</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -968,7 +968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX20"/>
+  <dimension ref="A1:AX21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -4018,10 +4018,8 @@
           <t>Pradip Poudel</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>9849120697</t>
-        </is>
+      <c r="O17" s="3" t="n">
+        <v>9849120697</v>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
@@ -4056,10 +4054,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y17" s="3" t="inlineStr">
-        <is>
-          <t>27.6655</t>
-        </is>
+      <c r="Y17" s="3" t="n">
+        <v>27.6655</v>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
@@ -4115,25 +4111,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN17" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN17" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
           <t>CDB927</t>
         </is>
       </c>
-      <c r="AP17" s="3" t="inlineStr">
-        <is>
-          <t>85.32093</t>
-        </is>
+      <c r="AP17" s="3" t="n">
+        <v>85.32093</v>
       </c>
       <c r="AQ17" s="3" t="inlineStr"/>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
@@ -4234,10 +4226,8 @@
           <t>Hotel Parbat Samjhana</t>
         </is>
       </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>9851322044</t>
-        </is>
+      <c r="O18" s="3" t="n">
+        <v>9851322044</v>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
@@ -4272,10 +4262,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y18" s="3" t="inlineStr">
-        <is>
-          <t>27.73037</t>
-        </is>
+      <c r="Y18" s="3" t="n">
+        <v>27.73037</v>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
@@ -4331,25 +4319,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN18" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN18" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
           <t>L33-2</t>
         </is>
       </c>
-      <c r="AP18" s="3" t="inlineStr">
-        <is>
-          <t>85.31158</t>
-        </is>
+      <c r="AP18" s="3" t="n">
+        <v>85.31158000000001</v>
       </c>
       <c r="AQ18" s="3" t="inlineStr"/>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI6 Router Upgrade   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">
@@ -4450,10 +4434,8 @@
           <t>Hotel Parbat Samjhana</t>
         </is>
       </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>9851322044</t>
-        </is>
+      <c r="O19" s="3" t="n">
+        <v>9851322044</v>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
@@ -4488,10 +4470,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y19" s="3" t="inlineStr">
-        <is>
-          <t>27.73029</t>
-        </is>
+      <c r="Y19" s="3" t="n">
+        <v>27.73029</v>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
@@ -4547,25 +4527,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN19" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN19" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
           <t>L33-2</t>
         </is>
       </c>
-      <c r="AP19" s="3" t="inlineStr">
-        <is>
-          <t>85.31154</t>
-        </is>
+      <c r="AP19" s="3" t="n">
+        <v>85.31153999999999</v>
       </c>
       <c r="AQ19" s="3" t="inlineStr"/>
       <c r="AR19" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6 Router Upgrade   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS19" s="3" t="inlineStr">
@@ -4666,10 +4642,8 @@
           <t>Rajiv Pandey</t>
         </is>
       </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t>9745326628</t>
-        </is>
+      <c r="O20" s="3" t="n">
+        <v>9745326628</v>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
@@ -4704,10 +4678,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y20" s="3" t="inlineStr">
-        <is>
-          <t>27.67518</t>
-        </is>
+      <c r="Y20" s="3" t="n">
+        <v>27.67518</v>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
@@ -4759,47 +4731,43 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN20" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN20" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
           <t>3,14</t>
         </is>
       </c>
-      <c r="AP20" s="3" t="inlineStr">
-        <is>
-          <t>85.378529</t>
-        </is>
+      <c r="AP20" s="3" t="n">
+        <v>85.378529</v>
       </c>
       <c r="AQ20" s="3" t="inlineStr"/>
       <c r="AR20" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
+        <is>
+          <t>1d 49m</t>
+        </is>
+      </c>
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>1d 49m</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV20" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS20" s="3" t="inlineStr">
-        <is>
-          <t>1d 49m</t>
-        </is>
-      </c>
-      <c r="AT20" s="3" t="inlineStr">
-        <is>
-          <t>1d 49m</t>
-        </is>
-      </c>
-      <c r="AU20" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV20" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW20" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -4808,6 +4776,214 @@
       <c r="AX20" s="3" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 11:49 AM</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>TKT1380168</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>Ravi  Bajracharya</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>Ravi  Bajracharya</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>9841750330</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 11:49:48 AM</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="inlineStr"/>
+      <c r="T21" s="3" t="inlineStr"/>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>LTP9841750330</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 12:28:42 PM</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 11:49:48 AM</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y21" s="3" t="inlineStr"/>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA21" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB21" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC21" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD21" s="3" t="inlineStr"/>
+      <c r="AE21" s="3" t="inlineStr">
+        <is>
+          <t>Lagan khel (Kumari pati vanda ali mathi), Lalitpur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF21" s="3" t="inlineStr">
+        <is>
+          <t>ravibajracharya7@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG21" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH21" s="3" t="inlineStr"/>
+      <c r="AI21" s="3" t="inlineStr">
+        <is>
+          <t>19:21 hour</t>
+        </is>
+      </c>
+      <c r="AJ21" s="3" t="inlineStr"/>
+      <c r="AK21" s="3" t="inlineStr"/>
+      <c r="AL21" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM21" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN21" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO21" s="3" t="inlineStr">
+        <is>
+          <t>CDB923</t>
+        </is>
+      </c>
+      <c r="AP21" s="3" t="inlineStr"/>
+      <c r="AQ21" s="3" t="inlineStr"/>
+      <c r="AR21" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 21m</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV21" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW21" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX21" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Oct_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>70.8%</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -688,42 +688,65 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="B4" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>88.9%</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>45.0%</t>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>90.0%</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>41.7%</t>
         </is>
       </c>
     </row>
@@ -738,15 +761,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -757,25 +781,30 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -788,47 +817,53 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>4</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="F2" s="6" t="n">
-        <v>9</v>
+      <c r="F2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>IPTV Remote damage Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="F3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="6" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>IPTV Remote damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -838,13 +873,16 @@
         <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="6" t="n">
+      <c r="F4" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -860,12 +898,15 @@
         <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="F5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="G5" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -885,9 +926,12 @@
         <v>0</v>
       </c>
       <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="G6" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -907,9 +951,12 @@
         <v>0</v>
       </c>
       <c r="E7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="G7" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -923,38 +970,69 @@
         <v>0</v>
       </c>
       <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="F8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Replace SKYCOM to NETTV</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B10" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="C10" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="E10" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="F10" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="F9" s="4" t="n">
-        <v>16</v>
+      <c r="G10" s="4" t="n">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -968,7 +1046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX21"/>
+  <dimension ref="A1:AX25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -981,10 +1059,10 @@
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="34" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="42" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="34" customWidth="1" min="14" max="14"/>
+    <col width="42" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -998,11 +1076,11 @@
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
-    <col width="17" customWidth="1" min="28" max="28"/>
+    <col width="28" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="29" customWidth="1" min="32" max="32"/>
+    <col width="30" customWidth="1" min="32" max="32"/>
     <col width="39" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -1017,7 +1095,7 @@
     <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
-    <col width="32" customWidth="1" min="47" max="47"/>
+    <col width="36" customWidth="1" min="47" max="47"/>
     <col width="45" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
     <col width="23" customWidth="1" min="50" max="50"/>
@@ -4846,10 +4924,8 @@
           <t>Ravi  Bajracharya</t>
         </is>
       </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>9841750330</t>
-        </is>
+      <c r="O21" s="3" t="n">
+        <v>9841750330</v>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
@@ -4939,10 +5015,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN21" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN21" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
@@ -4953,37 +5027,897 @@
       <c r="AQ21" s="3" t="inlineStr"/>
       <c r="AR21" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 21m</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV21" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS21" s="3" t="inlineStr">
+      <c r="AW21" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX21" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:03 PM</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Case : STB return  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>STB return</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>TKT1380048</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>Kriti Shakya</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>Kriti Shakya</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>9841538314</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr"/>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:03:39 PM</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="inlineStr"/>
+      <c r="T22" s="3" t="inlineStr"/>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t>9841538314</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 11:01:01 AM</t>
+        </is>
+      </c>
+      <c r="W22" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:03:39 PM</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y22" s="3" t="inlineStr">
+        <is>
+          <t>27.661455</t>
+        </is>
+      </c>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA22" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB22" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC22" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD22" s="3" t="inlineStr"/>
+      <c r="AE22" s="3" t="inlineStr">
+        <is>
+          <t>Army Physical Training and Sports Centre, Lalitpur 4470044700, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF22" s="3" t="inlineStr"/>
+      <c r="AG22" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH22" s="3" t="inlineStr"/>
+      <c r="AI22" s="3" t="inlineStr">
+        <is>
+          <t>21:02 hour</t>
+        </is>
+      </c>
+      <c r="AJ22" s="3" t="inlineStr"/>
+      <c r="AK22" s="3" t="inlineStr"/>
+      <c r="AL22" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM22" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN22" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO22" s="3" t="inlineStr">
+        <is>
+          <t>CDB946</t>
+        </is>
+      </c>
+      <c r="AP22" s="3" t="inlineStr">
+        <is>
+          <t>85.323686</t>
+        </is>
+      </c>
+      <c r="AQ22" s="3" t="inlineStr"/>
+      <c r="AR22" s="3" t="inlineStr">
+        <is>
+          <t>Case : STB return  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS22" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT21" s="3" t="inlineStr">
-        <is>
-          <t>1d 23h 21m</t>
-        </is>
-      </c>
-      <c r="AU21" s="3" t="inlineStr">
+      <c r="AT22" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 2m</t>
+        </is>
+      </c>
+      <c r="AU22" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV21" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="AW21" s="3" t="inlineStr">
+      <c r="AV22" s="3" t="inlineStr">
+        <is>
+          <t>Case : STB return  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX22" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:06 PM</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Case : sky to NETTV  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>sky to NETTV</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379566</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>Preeti Bajracharya</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>Preeti Bajracharya</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>9841384000</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr"/>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:11:34 PM</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="inlineStr"/>
+      <c r="T23" s="3" t="inlineStr"/>
+      <c r="U23" s="3" t="inlineStr">
+        <is>
+          <t>9841384000</t>
+        </is>
+      </c>
+      <c r="V23" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 06:19:57 PM</t>
+        </is>
+      </c>
+      <c r="W23" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:11:34 PM</t>
+        </is>
+      </c>
+      <c r="X23" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y23" s="3" t="inlineStr">
+        <is>
+          <t>27.69575</t>
+        </is>
+      </c>
+      <c r="Z23" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA23" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB23" s="3" t="inlineStr">
+        <is>
+          <t>customer experience sales</t>
+        </is>
+      </c>
+      <c r="AC23" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD23" s="3" t="inlineStr"/>
+      <c r="AE23" s="3" t="inlineStr">
+        <is>
+          <t>Teku Pachali Galli, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF23" s="3" t="inlineStr">
+        <is>
+          <t>preetibajracharya@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG23" s="3" t="inlineStr">
+        <is>
+          <t>Replace SKYCOM to NETTV</t>
+        </is>
+      </c>
+      <c r="AH23" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI23" s="3" t="inlineStr"/>
+      <c r="AJ23" s="3" t="inlineStr"/>
+      <c r="AK23" s="3" t="inlineStr"/>
+      <c r="AL23" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM23" s="3" t="inlineStr">
+        <is>
+          <t>Yaman Bhandari</t>
+        </is>
+      </c>
+      <c r="AN23" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO23" s="3" t="inlineStr">
+        <is>
+          <t>CDB044</t>
+        </is>
+      </c>
+      <c r="AP23" s="3" t="inlineStr">
+        <is>
+          <t>85.30426</t>
+        </is>
+      </c>
+      <c r="AQ23" s="3" t="inlineStr"/>
+      <c r="AR23" s="3" t="inlineStr">
+        <is>
+          <t>Case : sky to NETTV  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS23" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT23" s="3" t="inlineStr">
+        <is>
+          <t>2d 17h 51m</t>
+        </is>
+      </c>
+      <c r="AU23" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV23" s="3" t="inlineStr">
+        <is>
+          <t>Case : sky to NETTV  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW23" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX23" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:05 PM</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : remote issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>remote issue</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379980</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>Sujan Amatya</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>Sujan Amatya</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>9860558291</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr"/>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:05:15 PM</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr"/>
+      <c r="T24" s="3" t="inlineStr"/>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t>9860558291</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 10:25:07 AM</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:05:15 PM</t>
+        </is>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y24" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA24" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB24" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC24" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD24" s="3" t="inlineStr"/>
+      <c r="AE24" s="3" t="inlineStr">
+        <is>
+          <t>Basantapur Near Shree Kumari Secondary School, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF24" s="3" t="inlineStr">
+        <is>
+          <t>sujanamatya46@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG24" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Remote damage Issue</t>
+        </is>
+      </c>
+      <c r="AH24" s="3" t="inlineStr"/>
+      <c r="AI24" s="3" t="inlineStr">
+        <is>
+          <t>21:40 hour</t>
+        </is>
+      </c>
+      <c r="AJ24" s="3" t="inlineStr"/>
+      <c r="AK24" s="3" t="inlineStr"/>
+      <c r="AL24" s="3" t="inlineStr">
+        <is>
+          <t>Sanish Magar</t>
+        </is>
+      </c>
+      <c r="AM24" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN24" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO24" s="3" t="inlineStr">
+        <is>
+          <t>CDB025</t>
+        </is>
+      </c>
+      <c r="AP24" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ24" s="3" t="inlineStr"/>
+      <c r="AR24" s="3" t="inlineStr">
+        <is>
+          <t>Case : remote issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS24" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT24" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 40m</t>
+        </is>
+      </c>
+      <c r="AU24" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV24" s="3" t="inlineStr">
+        <is>
+          <t>Case : remote issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX24" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:04 PM</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>TKT1378950</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>Victim Support &amp; Rehalibitation Program</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>Victim Support &amp; Rehalibitation Program</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>9841345531</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr"/>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:04:18 PM</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr"/>
+      <c r="T25" s="3" t="inlineStr"/>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t>9841345531</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 10:47:59 AM</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:04:18 PM</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="inlineStr">
+        <is>
+          <t>27.723737</t>
+        </is>
+      </c>
+      <c r="Z25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA25" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB25" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC25" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD25" s="3" t="inlineStr"/>
+      <c r="AE25" s="3" t="inlineStr">
+        <is>
+          <t>Tekkon Technologies,Shree Marga, Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF25" s="3" t="inlineStr">
+        <is>
+          <t>prakashtamang@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG25" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH25" s="3" t="inlineStr"/>
+      <c r="AI25" s="3" t="inlineStr">
+        <is>
+          <t>07:17 hour</t>
+        </is>
+      </c>
+      <c r="AJ25" s="3" t="inlineStr"/>
+      <c r="AK25" s="3" t="inlineStr"/>
+      <c r="AL25" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM25" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN25" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO25" s="3" t="inlineStr">
+        <is>
+          <t>2,16</t>
+        </is>
+      </c>
+      <c r="AP25" s="3" t="inlineStr">
+        <is>
+          <t>85.324953</t>
+        </is>
+      </c>
+      <c r="AQ25" s="3" t="inlineStr"/>
+      <c r="AR25" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS25" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT25" s="3" t="inlineStr">
+        <is>
+          <t>3d 1h 16m</t>
+        </is>
+      </c>
+      <c r="AU25" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV25" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW25" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX21" s="3" t="inlineStr">
-        <is>
-          <t>Rajesh Maharjan</t>
+      <c r="AX25" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Oct_2026.xlsx
@@ -532,10 +532,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C5" s="3" t="n">
-        <v>4</v>
-      </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>70.8%</t>
+          <t>70.4%</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>14.8%</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>37.0%</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -838,11 +838,11 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>IPTV Remote damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>0</v>
@@ -854,20 +854,20 @@
         <v>1</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>IPTV Remote damage Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0</v>
@@ -879,7 +879,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>2</v>
@@ -888,7 +888,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB Adaptor damage Issue</t>
+          <t>ONT and Setup Box Recovery</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -901,10 +901,10 @@
         <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>1</v>
@@ -913,7 +913,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>ONT and Setup Box Recovery</t>
+          <t>IPTV STB Adaptor damage Issue</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -926,10 +926,10 @@
         <v>0</v>
       </c>
       <c r="E6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>1</v>
@@ -1011,28 +1011,53 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C10" s="4" t="n">
+      <c r="B11" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D11" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E11" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="F10" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>20</v>
+      <c r="G11" s="4" t="n">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -1046,7 +1071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX25"/>
+  <dimension ref="A1:AX28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1086,7 +1111,7 @@
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="20" customWidth="1" min="38" max="38"/>
+    <col width="28" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
@@ -5128,10 +5153,8 @@
           <t>Kriti Shakya</t>
         </is>
       </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>9841538314</t>
-        </is>
+      <c r="O22" s="3" t="n">
+        <v>9841538314</v>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
@@ -5166,10 +5189,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y22" s="3" t="inlineStr">
-        <is>
-          <t>27.661455</t>
-        </is>
+      <c r="Y22" s="3" t="n">
+        <v>27.661455</v>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
@@ -5221,25 +5242,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN22" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN22" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
           <t>CDB946</t>
         </is>
       </c>
-      <c r="AP22" s="3" t="inlineStr">
-        <is>
-          <t>85.323686</t>
-        </is>
+      <c r="AP22" s="3" t="n">
+        <v>85.323686</v>
       </c>
       <c r="AQ22" s="3" t="inlineStr"/>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>Case : STB return  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
@@ -5340,10 +5357,8 @@
           <t>Preeti Bajracharya</t>
         </is>
       </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t>9841384000</t>
-        </is>
+      <c r="O23" s="3" t="n">
+        <v>9841384000</v>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
@@ -5378,10 +5393,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y23" s="3" t="inlineStr">
-        <is>
-          <t>27.69575</t>
-        </is>
+      <c r="Y23" s="3" t="n">
+        <v>27.69575</v>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
@@ -5419,10 +5432,8 @@
           <t>Replace SKYCOM to NETTV</t>
         </is>
       </c>
-      <c r="AH23" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH23" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI23" s="3" t="inlineStr"/>
       <c r="AJ23" s="3" t="inlineStr"/>
@@ -5437,25 +5448,21 @@
           <t>Yaman Bhandari</t>
         </is>
       </c>
-      <c r="AN23" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN23" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
           <t>CDB044</t>
         </is>
       </c>
-      <c r="AP23" s="3" t="inlineStr">
-        <is>
-          <t>85.30426</t>
-        </is>
+      <c r="AP23" s="3" t="n">
+        <v>85.30426</v>
       </c>
       <c r="AQ23" s="3" t="inlineStr"/>
       <c r="AR23" s="3" t="inlineStr">
         <is>
-          <t>Case : sky to NETTV  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS23" s="3" t="inlineStr">
@@ -5556,10 +5563,8 @@
           <t>Sujan Amatya</t>
         </is>
       </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t>9860558291</t>
-        </is>
+      <c r="O24" s="3" t="n">
+        <v>9860558291</v>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
@@ -5594,10 +5599,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y24" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y24" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
@@ -5653,25 +5656,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN24" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN24" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
           <t>CDB025</t>
         </is>
       </c>
-      <c r="AP24" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP24" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ24" s="3" t="inlineStr"/>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>Case : remote issue  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
@@ -5772,10 +5771,8 @@
           <t>Victim Support &amp; Rehalibitation Program</t>
         </is>
       </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t>9841345531</t>
-        </is>
+      <c r="O25" s="3" t="n">
+        <v>9841345531</v>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
@@ -5810,10 +5807,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y25" s="3" t="inlineStr">
-        <is>
-          <t>27.723737</t>
-        </is>
+      <c r="Y25" s="3" t="n">
+        <v>27.723737</v>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
@@ -5869,53 +5864,669 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN25" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN25" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
           <t>2,16</t>
         </is>
       </c>
-      <c r="AP25" s="3" t="inlineStr">
-        <is>
-          <t>85.324953</t>
-        </is>
+      <c r="AP25" s="3" t="n">
+        <v>85.32495299999999</v>
       </c>
       <c r="AQ25" s="3" t="inlineStr"/>
       <c r="AR25" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS25" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT25" s="3" t="inlineStr">
+        <is>
+          <t>3d 1h 16m</t>
+        </is>
+      </c>
+      <c r="AU25" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV25" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS25" s="3" t="inlineStr">
+      <c r="AW25" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX25" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:30 PM</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>IPTV issue</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>TKT1380003</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>Prabat Bhandari</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>Prabat Bhandari</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t>9851089669</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr"/>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:30:13 PM</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr"/>
+      <c r="T26" s="3" t="inlineStr"/>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t>9851089669</t>
+        </is>
+      </c>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 10:32:40 AM</t>
+        </is>
+      </c>
+      <c r="W26" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:30:13 PM</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y26" s="3" t="inlineStr"/>
+      <c r="Z26" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA26" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB26" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC26" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD26" s="3" t="inlineStr"/>
+      <c r="AE26" s="3" t="inlineStr">
+        <is>
+          <t>27.676569404736984,85.36483187861175, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF26" s="3" t="inlineStr"/>
+      <c r="AG26" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="AH26" s="3" t="inlineStr"/>
+      <c r="AI26" s="3" t="inlineStr">
+        <is>
+          <t>21:58 hour</t>
+        </is>
+      </c>
+      <c r="AJ26" s="3" t="inlineStr"/>
+      <c r="AK26" s="3" t="inlineStr"/>
+      <c r="AL26" s="3" t="inlineStr">
+        <is>
+          <t>Rahul Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM26" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN26" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO26" s="3" t="inlineStr">
+        <is>
+          <t>L21-8</t>
+        </is>
+      </c>
+      <c r="AP26" s="3" t="inlineStr"/>
+      <c r="AQ26" s="3" t="inlineStr"/>
+      <c r="AR26" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS26" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT25" s="3" t="inlineStr">
-        <is>
-          <t>3d 1h 16m</t>
-        </is>
-      </c>
-      <c r="AU25" s="3" t="inlineStr">
+      <c r="AT26" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 57m</t>
+        </is>
+      </c>
+      <c r="AU26" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV25" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="AW25" s="3" t="inlineStr">
-        <is>
-          <t>WiFi 6 Upgrade</t>
-        </is>
-      </c>
-      <c r="AX25" s="3" t="inlineStr">
+      <c r="AV26" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW26" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX26" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:27 PM</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv setbox issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>iptv setbox issue</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>TKT1380270</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>Habib Laheri</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>Habib Laheri</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>9851029384</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr"/>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 01:32:11 PM</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr"/>
+      <c r="T27" s="3" t="inlineStr"/>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
+          <t>IC9851029384A</t>
+        </is>
+      </c>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 01:28:56 PM</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:27:49 PM</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y27" s="3" t="inlineStr">
+        <is>
+          <t>27.70816</t>
+        </is>
+      </c>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA27" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB27" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC27" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD27" s="3" t="inlineStr"/>
+      <c r="AE27" s="3" t="inlineStr">
+        <is>
+          <t>Asan near to balkumari madir, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF27" s="3" t="inlineStr"/>
+      <c r="AG27" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH27" s="3" t="inlineStr"/>
+      <c r="AI27" s="3" t="inlineStr"/>
+      <c r="AJ27" s="3" t="inlineStr"/>
+      <c r="AK27" s="3" t="inlineStr"/>
+      <c r="AL27" s="3" t="inlineStr">
+        <is>
+          <t>Roshan Yadav (L1 Support)</t>
+        </is>
+      </c>
+      <c r="AM27" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN27" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO27" s="3" t="inlineStr">
+        <is>
+          <t>3,13</t>
+        </is>
+      </c>
+      <c r="AP27" s="3" t="inlineStr">
+        <is>
+          <t>85.31304</t>
+        </is>
+      </c>
+      <c r="AQ27" s="3" t="inlineStr"/>
+      <c r="AR27" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv setbox issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS27" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 55m</t>
+        </is>
+      </c>
+      <c r="AT27" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 58m</t>
+        </is>
+      </c>
+      <c r="AU27" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV27" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv setbox issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW27" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX27" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:26 PM</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>iptv issue</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>TKT1381481</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>Sita Subedi</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>Sita Subedi</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t>9841184071</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q28" s="3" t="inlineStr"/>
+      <c r="R28" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:26:07 PM</t>
+        </is>
+      </c>
+      <c r="S28" s="3" t="inlineStr"/>
+      <c r="T28" s="3" t="inlineStr"/>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t>CHB9841184071</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 04:15:05 PM</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:26:07 PM</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y28" s="3" t="inlineStr"/>
+      <c r="Z28" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA28" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB28" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC28" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD28" s="3" t="inlineStr"/>
+      <c r="AE28" s="3" t="inlineStr">
+        <is>
+          <t>Yangalchowk,  Bhotebahal, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF28" s="3" t="inlineStr">
+        <is>
+          <t>9841184071@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG28" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH28" s="3" t="inlineStr"/>
+      <c r="AI28" s="3" t="inlineStr">
+        <is>
+          <t>06:11 hour</t>
+        </is>
+      </c>
+      <c r="AJ28" s="3" t="inlineStr"/>
+      <c r="AK28" s="3" t="inlineStr"/>
+      <c r="AL28" s="3" t="inlineStr">
+        <is>
+          <t>Pramila Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM28" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN28" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO28" s="3" t="inlineStr">
+        <is>
+          <t>CDB022</t>
+        </is>
+      </c>
+      <c r="AP28" s="3" t="inlineStr"/>
+      <c r="AQ28" s="3" t="inlineStr"/>
+      <c r="AR28" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS28" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT28" s="3" t="inlineStr">
+        <is>
+          <t>20h 11m</t>
+        </is>
+      </c>
+      <c r="AU28" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV28" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW28" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX28" s="3" t="inlineStr">
         <is>
           <t>Chandramani Tharu</t>
         </is>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Oct_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
     </row>
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>4</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -688,19 +688,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>8</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>72.7%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>36.7%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>13.3%</t>
         </is>
       </c>
     </row>
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>9</v>
-      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>36.7%</t>
         </is>
       </c>
     </row>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>4</v>
@@ -832,7 +832,7 @@
         <v>1</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>0</v>
@@ -857,7 +857,7 @@
         <v>1</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -1042,10 +1042,10 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C11" s="4" t="n">
         <v>5</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>4</v>
       </c>
       <c r="D11" s="4" t="n">
         <v>5</v>
@@ -1057,7 +1057,7 @@
         <v>4</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1071,7 +1071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX28"/>
+  <dimension ref="A1:AX31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -5979,10 +5979,8 @@
           <t>Prabat Bhandari</t>
         </is>
       </c>
-      <c r="O26" s="3" t="inlineStr">
-        <is>
-          <t>9851089669</t>
-        </is>
+      <c r="O26" s="3" t="n">
+        <v>9851089669</v>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
@@ -6068,10 +6066,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN26" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN26" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO26" s="3" t="inlineStr">
         <is>
@@ -6082,7 +6078,7 @@
       <c r="AQ26" s="3" t="inlineStr"/>
       <c r="AR26" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV issue  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS26" s="3" t="inlineStr">
@@ -6183,10 +6179,8 @@
           <t>Habib Laheri</t>
         </is>
       </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t>9851029384</t>
-        </is>
+      <c r="O27" s="3" t="n">
+        <v>9851029384</v>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
@@ -6221,10 +6215,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y27" s="3" t="inlineStr">
-        <is>
-          <t>27.70816</t>
-        </is>
+      <c r="Y27" s="3" t="n">
+        <v>27.70816</v>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
@@ -6272,25 +6264,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN27" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN27" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
           <t>3,13</t>
         </is>
       </c>
-      <c r="AP27" s="3" t="inlineStr">
-        <is>
-          <t>85.31304</t>
-        </is>
+      <c r="AP27" s="3" t="n">
+        <v>85.31304</v>
       </c>
       <c r="AQ27" s="3" t="inlineStr"/>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv setbox issue  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
@@ -6391,10 +6379,8 @@
           <t>Sita Subedi</t>
         </is>
       </c>
-      <c r="O28" s="3" t="inlineStr">
-        <is>
-          <t>9841184071</t>
-        </is>
+      <c r="O28" s="3" t="n">
+        <v>9841184071</v>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
@@ -6484,10 +6470,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN28" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN28" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO28" s="3" t="inlineStr">
         <is>
@@ -6498,35 +6482,655 @@
       <c r="AQ28" s="3" t="inlineStr"/>
       <c r="AR28" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS28" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT28" s="3" t="inlineStr">
+        <is>
+          <t>20h 11m</t>
+        </is>
+      </c>
+      <c r="AU28" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV28" s="3" t="inlineStr">
+        <is>
           <t>Case : iptv issue  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS28" s="3" t="inlineStr">
+      <c r="AW28" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX28" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:41 PM</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>TKT1380887</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>Ushan Dev Shakya</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>Ushan Dev Shakya</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>9803034566</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr"/>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:41:06 PM</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr"/>
+      <c r="T29" s="3" t="inlineStr"/>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t>9803034566</t>
+        </is>
+      </c>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 07:48:25 AM</t>
+        </is>
+      </c>
+      <c r="W29" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:41:06 PM</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y29" s="3" t="inlineStr">
+        <is>
+          <t>27.66594</t>
+        </is>
+      </c>
+      <c r="Z29" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA29" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB29" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC29" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD29" s="3" t="inlineStr"/>
+      <c r="AE29" s="3" t="inlineStr">
+        <is>
+          <t>Machaga, Lunkhusi Near BNB hospital, near star food land, , Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF29" s="3" t="inlineStr">
+        <is>
+          <t>usnshakya4@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG29" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH29" s="3" t="inlineStr"/>
+      <c r="AI29" s="3" t="inlineStr">
+        <is>
+          <t>12:41 hour</t>
+        </is>
+      </c>
+      <c r="AJ29" s="3" t="inlineStr"/>
+      <c r="AK29" s="3" t="inlineStr"/>
+      <c r="AL29" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM29" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN29" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO29" s="3" t="inlineStr">
+        <is>
+          <t>CDB962</t>
+        </is>
+      </c>
+      <c r="AP29" s="3" t="inlineStr">
+        <is>
+          <t>85.33006</t>
+        </is>
+      </c>
+      <c r="AQ29" s="3" t="inlineStr"/>
+      <c r="AR29" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS29" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT28" s="3" t="inlineStr">
-        <is>
-          <t>20h 11m</t>
-        </is>
-      </c>
-      <c r="AU28" s="3" t="inlineStr">
+      <c r="AT29" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 52m</t>
+        </is>
+      </c>
+      <c r="AU29" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV28" s="3" t="inlineStr">
-        <is>
-          <t>Case : iptv issue  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="AW28" s="3" t="inlineStr">
-        <is>
-          <t>IPTV Issue</t>
-        </is>
-      </c>
-      <c r="AX28" s="3" t="inlineStr">
+      <c r="AV29" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW29" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX29" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:36 PM</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr"/>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Case : red light issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>red light issue</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>TKT1380592</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>Rajkumar Deshar</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>Rajkumar Deshar</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t>9841400677</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q30" s="3" t="inlineStr"/>
+      <c r="R30" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 05:24:46 PM</t>
+        </is>
+      </c>
+      <c r="S30" s="3" t="inlineStr"/>
+      <c r="T30" s="3" t="inlineStr"/>
+      <c r="U30" s="3" t="inlineStr">
+        <is>
+          <t>9841400677</t>
+        </is>
+      </c>
+      <c r="V30" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 05:20:39 PM</t>
+        </is>
+      </c>
+      <c r="W30" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:36:33 PM</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y30" s="3" t="inlineStr"/>
+      <c r="Z30" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA30" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB30" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC30" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD30" s="3" t="inlineStr"/>
+      <c r="AE30" s="3" t="inlineStr">
+        <is>
+          <t>Kumari mandir, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF30" s="3" t="inlineStr"/>
+      <c r="AG30" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH30" s="3" t="inlineStr"/>
+      <c r="AI30" s="3" t="inlineStr"/>
+      <c r="AJ30" s="3" t="inlineStr"/>
+      <c r="AK30" s="3" t="inlineStr"/>
+      <c r="AL30" s="3" t="inlineStr">
+        <is>
+          <t>Ayush Basnet</t>
+        </is>
+      </c>
+      <c r="AM30" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN30" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO30" s="3" t="inlineStr">
+        <is>
+          <t>3,2</t>
+        </is>
+      </c>
+      <c r="AP30" s="3" t="inlineStr"/>
+      <c r="AQ30" s="3" t="inlineStr"/>
+      <c r="AR30" s="3" t="inlineStr">
+        <is>
+          <t>Case : red light issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS30" s="3" t="inlineStr">
+        <is>
+          <t>1d 19h 11m</t>
+        </is>
+      </c>
+      <c r="AT30" s="3" t="inlineStr">
+        <is>
+          <t>1d 19h 15m</t>
+        </is>
+      </c>
+      <c r="AU30" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV30" s="3" t="inlineStr">
+        <is>
+          <t>Case : red light issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX30" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:35 PM</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>TKT1378084</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>Raunak Maskay</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>Raunak Maskay</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t>9841126820</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q31" s="3" t="inlineStr"/>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 11:10:58 AM</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr"/>
+      <c r="T31" s="3" t="inlineStr"/>
+      <c r="U31" s="3" t="inlineStr">
+        <is>
+          <t>CHB9841126820</t>
+        </is>
+      </c>
+      <c r="V31" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 02:05:16 PM</t>
+        </is>
+      </c>
+      <c r="W31" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:35:00 PM</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y31" s="3" t="inlineStr"/>
+      <c r="Z31" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA31" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB31" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC31" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD31" s="3" t="inlineStr"/>
+      <c r="AE31" s="3" t="inlineStr">
+        <is>
+          <t>Bajaj Lainchaur (Star Auto Enterprises) Nagpokhari Marg, Kathmandu 44600, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF31" s="3" t="inlineStr">
+        <is>
+          <t>raunakmaskay@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG31" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH31" s="3" t="inlineStr"/>
+      <c r="AI31" s="3" t="inlineStr"/>
+      <c r="AJ31" s="3" t="inlineStr"/>
+      <c r="AK31" s="3" t="inlineStr"/>
+      <c r="AL31" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM31" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN31" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO31" s="3" t="inlineStr">
+        <is>
+          <t>CDB011</t>
+        </is>
+      </c>
+      <c r="AP31" s="3" t="inlineStr"/>
+      <c r="AQ31" s="3" t="inlineStr"/>
+      <c r="AR31" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS31" s="3" t="inlineStr">
+        <is>
+          <t>1h 24m</t>
+        </is>
+      </c>
+      <c r="AT31" s="3" t="inlineStr">
+        <is>
+          <t>3d 22h 29m</t>
+        </is>
+      </c>
+      <c r="AU31" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV31" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW31" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX31" s="3" t="inlineStr">
         <is>
           <t>Chandramani Tharu</t>
         </is>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Oct_2026.xlsx
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>4</v>
-      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>68.8%</t>
         </is>
       </c>
     </row>
@@ -688,19 +688,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>40.6%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>34.4%</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
         <v>5</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>1</v>
@@ -832,7 +832,7 @@
         <v>1</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -854,10 +854,10 @@
         <v>1</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -1048,16 +1048,16 @@
         <v>5</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>5</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1071,7 +1071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX31"/>
+  <dimension ref="A1:AX33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1105,7 +1105,7 @@
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="30" customWidth="1" min="32" max="32"/>
+    <col width="31" customWidth="1" min="32" max="32"/>
     <col width="39" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -6583,10 +6583,8 @@
           <t>Ushan Dev Shakya</t>
         </is>
       </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t>9803034566</t>
-        </is>
+      <c r="O29" s="3" t="n">
+        <v>9803034566</v>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
@@ -6621,10 +6619,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y29" s="3" t="inlineStr">
-        <is>
-          <t>27.66594</t>
-        </is>
+      <c r="Y29" s="3" t="n">
+        <v>27.66594</v>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
@@ -6680,25 +6676,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN29" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN29" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
           <t>CDB962</t>
         </is>
       </c>
-      <c r="AP29" s="3" t="inlineStr">
-        <is>
-          <t>85.33006</t>
-        </is>
+      <c r="AP29" s="3" t="n">
+        <v>85.33006</v>
       </c>
       <c r="AQ29" s="3" t="inlineStr"/>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
@@ -6799,10 +6791,8 @@
           <t>Rajkumar Deshar</t>
         </is>
       </c>
-      <c r="O30" s="3" t="inlineStr">
-        <is>
-          <t>9841400677</t>
-        </is>
+      <c r="O30" s="3" t="n">
+        <v>9841400677</v>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
@@ -6884,10 +6874,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN30" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN30" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
@@ -6898,7 +6886,7 @@
       <c r="AQ30" s="3" t="inlineStr"/>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>Case : red light issue  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
@@ -6999,10 +6987,8 @@
           <t>Raunak Maskay</t>
         </is>
       </c>
-      <c r="O31" s="3" t="inlineStr">
-        <is>
-          <t>9841126820</t>
-        </is>
+      <c r="O31" s="3" t="n">
+        <v>9841126820</v>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
@@ -7088,10 +7074,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN31" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN31" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
@@ -7102,29 +7086,29 @@
       <c r="AQ31" s="3" t="inlineStr"/>
       <c r="AR31" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS31" s="3" t="inlineStr">
+        <is>
+          <t>1h 24m</t>
+        </is>
+      </c>
+      <c r="AT31" s="3" t="inlineStr">
+        <is>
+          <t>3d 22h 29m</t>
+        </is>
+      </c>
+      <c r="AU31" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV31" s="3" t="inlineStr">
+        <is>
           <t>Case : Router Upgrade   has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS31" s="3" t="inlineStr">
-        <is>
-          <t>1h 24m</t>
-        </is>
-      </c>
-      <c r="AT31" s="3" t="inlineStr">
-        <is>
-          <t>3d 22h 29m</t>
-        </is>
-      </c>
-      <c r="AU31" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV31" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router Upgrade   has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
       <c r="AW31" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
@@ -7133,6 +7117,438 @@
       <c r="AX31" s="3" t="inlineStr">
         <is>
           <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:59 PM</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr"/>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgarde   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgarde</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379172</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>Bikash Thapaliya</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>Bikash Thapaliya</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t>9841873614</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr"/>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:59:37 PM</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="inlineStr"/>
+      <c r="T32" s="3" t="inlineStr"/>
+      <c r="U32" s="3" t="inlineStr">
+        <is>
+          <t>9841873614</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 01:30:41 PM</t>
+        </is>
+      </c>
+      <c r="W32" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:59:37 PM</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y32" s="3" t="inlineStr">
+        <is>
+          <t>27.73875</t>
+        </is>
+      </c>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA32" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB32" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC32" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD32" s="3" t="inlineStr"/>
+      <c r="AE32" s="3" t="inlineStr">
+        <is>
+          <t>jiban khatiwada homestay - Wholesaler Q852+G4G Tarakeshwar, Bagmati Province 44600, Kathmandu, Nepal</t>
+        </is>
+      </c>
+      <c r="AF32" s="3" t="inlineStr">
+        <is>
+          <t>bikashthapaliya123@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG32" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH32" s="3" t="inlineStr"/>
+      <c r="AI32" s="3" t="inlineStr">
+        <is>
+          <t>05:29 hour</t>
+        </is>
+      </c>
+      <c r="AJ32" s="3" t="inlineStr"/>
+      <c r="AK32" s="3" t="inlineStr"/>
+      <c r="AL32" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM32" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN32" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO32" s="3" t="inlineStr">
+        <is>
+          <t>L10-1</t>
+        </is>
+      </c>
+      <c r="AP32" s="3" t="inlineStr">
+        <is>
+          <t>85.30291</t>
+        </is>
+      </c>
+      <c r="AQ32" s="3" t="inlineStr"/>
+      <c r="AR32" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgarde   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS32" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT32" s="3" t="inlineStr">
+        <is>
+          <t>2d 23h 28m</t>
+        </is>
+      </c>
+      <c r="AU32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV32" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgarde   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX32" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:59 PM</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr"/>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Case : TV issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>TV issue</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>TKT1381638</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>Cyrus Shrestha</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>Cyrus Shrestha</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>9861926855</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr"/>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 05:39:01 PM</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr"/>
+      <c r="T33" s="3" t="inlineStr"/>
+      <c r="U33" s="3" t="inlineStr">
+        <is>
+          <t>DRZ9861926855</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 05:39:01 PM</t>
+        </is>
+      </c>
+      <c r="W33" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:59:25 PM</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y33" s="3" t="inlineStr">
+        <is>
+          <t>27.70284</t>
+        </is>
+      </c>
+      <c r="Z33" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA33" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB33" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC33" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD33" s="3" t="inlineStr"/>
+      <c r="AE33" s="3" t="inlineStr">
+        <is>
+          <t>Kalimati 27.7027679, 85.2861990 - Near Jehovah's Witnesses Society,Kalimati,Kathmandu - Kathmandu Me</t>
+        </is>
+      </c>
+      <c r="AF33" s="3" t="inlineStr">
+        <is>
+          <t>5sos.cyrus@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG33" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH33" s="3" t="inlineStr"/>
+      <c r="AI33" s="3" t="inlineStr">
+        <is>
+          <t>05:20 hour</t>
+        </is>
+      </c>
+      <c r="AJ33" s="3" t="inlineStr"/>
+      <c r="AK33" s="3" t="inlineStr"/>
+      <c r="AL33" s="3" t="inlineStr">
+        <is>
+          <t>Yaman Bhandari</t>
+        </is>
+      </c>
+      <c r="AM33" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN33" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO33" s="3" t="inlineStr">
+        <is>
+          <t>2,2</t>
+        </is>
+      </c>
+      <c r="AP33" s="3" t="inlineStr">
+        <is>
+          <t>85.2862</t>
+        </is>
+      </c>
+      <c r="AQ33" s="3" t="inlineStr"/>
+      <c r="AR33" s="3" t="inlineStr">
+        <is>
+          <t>Case : TV issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS33" s="3" t="inlineStr">
+        <is>
+          <t>19h 20m</t>
+        </is>
+      </c>
+      <c r="AT33" s="3" t="inlineStr">
+        <is>
+          <t>19h 20m</t>
+        </is>
+      </c>
+      <c r="AU33" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV33" s="3" t="inlineStr">
+        <is>
+          <t>Case : TV issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW33" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX33" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Oct_2026.xlsx
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>5</v>
-      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>85.7%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>69.7%</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>39.4%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.1%</t>
         </is>
       </c>
     </row>
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>10</v>
-      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>91.7%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>36.4%</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX33"/>
+  <dimension ref="A1:AX34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -7187,10 +7187,8 @@
           <t>Bikash Thapaliya</t>
         </is>
       </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t>9841873614</t>
-        </is>
+      <c r="O32" s="3" t="n">
+        <v>9841873614</v>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
@@ -7225,10 +7223,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y32" s="3" t="inlineStr">
-        <is>
-          <t>27.73875</t>
-        </is>
+      <c r="Y32" s="3" t="n">
+        <v>27.73875</v>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
@@ -7284,25 +7280,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN32" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN32" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
           <t>L10-1</t>
         </is>
       </c>
-      <c r="AP32" s="3" t="inlineStr">
-        <is>
-          <t>85.30291</t>
-        </is>
+      <c r="AP32" s="3" t="n">
+        <v>85.30291</v>
       </c>
       <c r="AQ32" s="3" t="inlineStr"/>
       <c r="AR32" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgarde   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS32" s="3" t="inlineStr">
@@ -7393,20 +7385,14 @@
           <t>Closed</t>
         </is>
       </c>
-      <c r="M33" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M33" s="3" t="inlineStr"/>
       <c r="N33" s="3" t="inlineStr">
         <is>
           <t>Cyrus Shrestha</t>
         </is>
       </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t>9861926855</t>
-        </is>
+      <c r="O33" s="3" t="n">
+        <v>9861926855</v>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
@@ -7441,10 +7427,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y33" s="3" t="inlineStr">
-        <is>
-          <t>27.70284</t>
-        </is>
+      <c r="Y33" s="3" t="n">
+        <v>27.70284</v>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
@@ -7500,47 +7484,43 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN33" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN33" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO33" s="3" t="inlineStr">
         <is>
           <t>2,2</t>
         </is>
       </c>
-      <c r="AP33" s="3" t="inlineStr">
-        <is>
-          <t>85.2862</t>
-        </is>
+      <c r="AP33" s="3" t="n">
+        <v>85.28619999999999</v>
       </c>
       <c r="AQ33" s="3" t="inlineStr"/>
       <c r="AR33" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS33" s="3" t="inlineStr">
+        <is>
+          <t>19h 20m</t>
+        </is>
+      </c>
+      <c r="AT33" s="3" t="inlineStr">
+        <is>
+          <t>19h 20m</t>
+        </is>
+      </c>
+      <c r="AU33" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV33" s="3" t="inlineStr">
+        <is>
           <t>Case : TV issue  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS33" s="3" t="inlineStr">
-        <is>
-          <t>19h 20m</t>
-        </is>
-      </c>
-      <c r="AT33" s="3" t="inlineStr">
-        <is>
-          <t>19h 20m</t>
-        </is>
-      </c>
-      <c r="AU33" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV33" s="3" t="inlineStr">
-        <is>
-          <t>Case : TV issue  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW33" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
@@ -7549,6 +7529,222 @@
       <c r="AX33" s="3" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 1:13 PM</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr"/>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 router upgrade</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>TKT1377993</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>Yubraj Bhattarai</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>Yubraj Bhattarai</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t>9851110377</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q34" s="3" t="inlineStr"/>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 01:13:33 PM</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="inlineStr"/>
+      <c r="T34" s="3" t="inlineStr"/>
+      <c r="U34" s="3" t="inlineStr">
+        <is>
+          <t>9851110377</t>
+        </is>
+      </c>
+      <c r="V34" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 12:14:38 PM</t>
+        </is>
+      </c>
+      <c r="W34" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 01:13:33 PM</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y34" s="3" t="inlineStr">
+        <is>
+          <t>27.73578</t>
+        </is>
+      </c>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA34" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB34" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC34" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD34" s="3" t="inlineStr"/>
+      <c r="AE34" s="3" t="inlineStr">
+        <is>
+          <t>near Fishery Development Directorate  Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF34" s="3" t="inlineStr">
+        <is>
+          <t>ewarajbhattarai@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG34" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH34" s="3" t="inlineStr"/>
+      <c r="AI34" s="3" t="inlineStr">
+        <is>
+          <t>09:13 hour</t>
+        </is>
+      </c>
+      <c r="AJ34" s="3" t="inlineStr"/>
+      <c r="AK34" s="3" t="inlineStr"/>
+      <c r="AL34" s="3" t="inlineStr">
+        <is>
+          <t>Mamata Bhujel</t>
+        </is>
+      </c>
+      <c r="AM34" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN34" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO34" s="3" t="inlineStr">
+        <is>
+          <t>1,10</t>
+        </is>
+      </c>
+      <c r="AP34" s="3" t="inlineStr">
+        <is>
+          <t>85.30316</t>
+        </is>
+      </c>
+      <c r="AQ34" s="3" t="inlineStr"/>
+      <c r="AR34" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS34" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>4d 58m</t>
+        </is>
+      </c>
+      <c r="AU34" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV34" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW34" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX34" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Oct_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>5</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>85.7%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C6" s="3" t="n">
-        <v>4</v>
-      </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>69.7%</t>
+          <t>70.3%</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>35.1%</t>
         </is>
       </c>
     </row>
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>13.5%</t>
         </is>
       </c>
     </row>
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>93.3%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>40.5%</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>5</v>
@@ -829,10 +829,10 @@
         <v>1</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>0</v>
@@ -857,7 +857,7 @@
         <v>2</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -1042,10 +1042,10 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D11" s="4" t="n">
         <v>6</v>
@@ -1054,10 +1054,10 @@
         <v>5</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1071,7 +1071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX34"/>
+  <dimension ref="A1:AX38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -7599,10 +7599,8 @@
           <t>Yubraj Bhattarai</t>
         </is>
       </c>
-      <c r="O34" s="3" t="inlineStr">
-        <is>
-          <t>9851110377</t>
-        </is>
+      <c r="O34" s="3" t="n">
+        <v>9851110377</v>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
@@ -7637,10 +7635,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y34" s="3" t="inlineStr">
-        <is>
-          <t>27.73578</t>
-        </is>
+      <c r="Y34" s="3" t="n">
+        <v>27.73578</v>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
@@ -7696,55 +7692,911 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN34" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN34" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO34" s="3" t="inlineStr">
         <is>
           <t>1,10</t>
         </is>
       </c>
-      <c r="AP34" s="3" t="inlineStr">
-        <is>
-          <t>85.30316</t>
-        </is>
+      <c r="AP34" s="3" t="n">
+        <v>85.30316000000001</v>
       </c>
       <c r="AQ34" s="3" t="inlineStr"/>
       <c r="AR34" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS34" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>4d 58m</t>
+        </is>
+      </c>
+      <c r="AU34" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV34" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6 router upgrade   has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS34" s="3" t="inlineStr">
+      <c r="AW34" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX34" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 1:30 PM</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379448</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>Roman Shrestha</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>Roman Shrestha</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t>9828559226</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr"/>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 01:30:27 PM</t>
+        </is>
+      </c>
+      <c r="S35" s="3" t="inlineStr"/>
+      <c r="T35" s="3" t="inlineStr"/>
+      <c r="U35" s="3" t="inlineStr">
+        <is>
+          <t>9828559226</t>
+        </is>
+      </c>
+      <c r="V35" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 04:54:07 PM</t>
+        </is>
+      </c>
+      <c r="W35" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 01:30:27 PM</t>
+        </is>
+      </c>
+      <c r="X35" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y35" s="3" t="inlineStr">
+        <is>
+          <t>27.67445</t>
+        </is>
+      </c>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA35" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB35" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC35" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD35" s="3" t="inlineStr"/>
+      <c r="AE35" s="3" t="inlineStr">
+        <is>
+          <t>Back town of Jyapu Samaj BhawanLonla Tole Marga,Balkumari,Lalitpur, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF35" s="3" t="inlineStr"/>
+      <c r="AG35" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH35" s="3" t="inlineStr"/>
+      <c r="AI35" s="3" t="inlineStr">
+        <is>
+          <t>02:36 hour</t>
+        </is>
+      </c>
+      <c r="AJ35" s="3" t="inlineStr"/>
+      <c r="AK35" s="3" t="inlineStr"/>
+      <c r="AL35" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM35" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN35" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO35" s="3" t="inlineStr">
+        <is>
+          <t>CDB635</t>
+        </is>
+      </c>
+      <c r="AP35" s="3" t="inlineStr">
+        <is>
+          <t>85.33265</t>
+        </is>
+      </c>
+      <c r="AQ35" s="3" t="inlineStr"/>
+      <c r="AR35" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS35" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT34" s="3" t="inlineStr">
-        <is>
-          <t>4d 58m</t>
-        </is>
-      </c>
-      <c r="AU34" s="3" t="inlineStr">
+      <c r="AT35" s="3" t="inlineStr">
+        <is>
+          <t>2d 20h 36m</t>
+        </is>
+      </c>
+      <c r="AU35" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV34" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6 router upgrade   has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="AW34" s="3" t="inlineStr">
+      <c r="AV35" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW35" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX34" s="3" t="inlineStr">
-        <is>
-          <t>Sanjeev Giri</t>
+      <c r="AX35" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 1:20 PM</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr"/>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv stb box faulty    has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>iptv stb box faulty</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>TKT1381457</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>Suresh Kumar</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>Suresh Kumar</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t>9812886249</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr"/>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 03:55:40 PM</t>
+        </is>
+      </c>
+      <c r="S36" s="3" t="inlineStr"/>
+      <c r="T36" s="3" t="inlineStr"/>
+      <c r="U36" s="3" t="inlineStr">
+        <is>
+          <t>9880141359</t>
+        </is>
+      </c>
+      <c r="V36" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 03:52:15 PM</t>
+        </is>
+      </c>
+      <c r="W36" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 01:20:50 PM</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y36" s="3" t="inlineStr">
+        <is>
+          <t>27.687738</t>
+        </is>
+      </c>
+      <c r="Z36" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA36" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB36" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC36" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD36" s="3" t="inlineStr"/>
+      <c r="AE36" s="3" t="inlineStr">
+        <is>
+          <t>Near KitabKalam Stationery MartKathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF36" s="3" t="inlineStr">
+        <is>
+          <t>harsh07042@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG36" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH36" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI36" s="3" t="inlineStr"/>
+      <c r="AJ36" s="3" t="inlineStr"/>
+      <c r="AK36" s="3" t="inlineStr"/>
+      <c r="AL36" s="3" t="inlineStr">
+        <is>
+          <t>Dinesh Rawat</t>
+        </is>
+      </c>
+      <c r="AM36" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN36" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO36" s="3" t="inlineStr">
+        <is>
+          <t>4,12</t>
+        </is>
+      </c>
+      <c r="AP36" s="3" t="inlineStr">
+        <is>
+          <t>85.297712</t>
+        </is>
+      </c>
+      <c r="AQ36" s="3" t="inlineStr"/>
+      <c r="AR36" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv stb box faulty    has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS36" s="3" t="inlineStr">
+        <is>
+          <t>21h 25m</t>
+        </is>
+      </c>
+      <c r="AT36" s="3" t="inlineStr">
+        <is>
+          <t>21h 28m</t>
+        </is>
+      </c>
+      <c r="AU36" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV36" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv stb box faulty    has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW36" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX36" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 1:27 PM</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr"/>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>TKT1380053</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>Keshab Rijal</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>Keshab Rijal</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t>9866316594</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr"/>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 11:04:29 AM</t>
+        </is>
+      </c>
+      <c r="S37" s="3" t="inlineStr"/>
+      <c r="T37" s="3" t="inlineStr"/>
+      <c r="U37" s="3" t="inlineStr">
+        <is>
+          <t>9866316594</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 11:04:29 AM</t>
+        </is>
+      </c>
+      <c r="W37" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 01:27:19 PM</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y37" s="3" t="inlineStr">
+        <is>
+          <t>27.695898</t>
+        </is>
+      </c>
+      <c r="Z37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA37" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB37" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC37" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD37" s="3" t="inlineStr"/>
+      <c r="AE37" s="3" t="inlineStr">
+        <is>
+          <t>Parikar Banquet 44600, Nepal, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF37" s="3" t="inlineStr">
+        <is>
+          <t>keshabrijal7987@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG37" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH37" s="3" t="inlineStr"/>
+      <c r="AI37" s="3" t="inlineStr">
+        <is>
+          <t>22:22 hour</t>
+        </is>
+      </c>
+      <c r="AJ37" s="3" t="inlineStr"/>
+      <c r="AK37" s="3" t="inlineStr"/>
+      <c r="AL37" s="3" t="inlineStr">
+        <is>
+          <t>Sabina K.C</t>
+        </is>
+      </c>
+      <c r="AM37" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN37" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO37" s="3" t="inlineStr">
+        <is>
+          <t>CDB218</t>
+        </is>
+      </c>
+      <c r="AP37" s="3" t="inlineStr">
+        <is>
+          <t>85.275775</t>
+        </is>
+      </c>
+      <c r="AQ37" s="3" t="inlineStr"/>
+      <c r="AR37" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS37" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 22m</t>
+        </is>
+      </c>
+      <c r="AT37" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 22m</t>
+        </is>
+      </c>
+      <c r="AU37" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV37" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW37" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX37" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 1:26 PM</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr"/>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>TKT1380053</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>Keshab Rijal</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>Keshab Rijal</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t>9866316594</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="inlineStr"/>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 11:04:29 AM</t>
+        </is>
+      </c>
+      <c r="S38" s="3" t="inlineStr"/>
+      <c r="T38" s="3" t="inlineStr"/>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t>9866316594</t>
+        </is>
+      </c>
+      <c r="V38" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 11:04:29 AM</t>
+        </is>
+      </c>
+      <c r="W38" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 01:27:19 PM</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y38" s="3" t="inlineStr">
+        <is>
+          <t>27.695898</t>
+        </is>
+      </c>
+      <c r="Z38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA38" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB38" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC38" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD38" s="3" t="inlineStr"/>
+      <c r="AE38" s="3" t="inlineStr">
+        <is>
+          <t>Parikar Banquet 44600, Nepal, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF38" s="3" t="inlineStr">
+        <is>
+          <t>keshabrijal7987@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG38" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH38" s="3" t="inlineStr"/>
+      <c r="AI38" s="3" t="inlineStr">
+        <is>
+          <t>22:22 hour</t>
+        </is>
+      </c>
+      <c r="AJ38" s="3" t="inlineStr"/>
+      <c r="AK38" s="3" t="inlineStr"/>
+      <c r="AL38" s="3" t="inlineStr">
+        <is>
+          <t>Sabina K.C</t>
+        </is>
+      </c>
+      <c r="AM38" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN38" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO38" s="3" t="inlineStr">
+        <is>
+          <t>CDB218</t>
+        </is>
+      </c>
+      <c r="AP38" s="3" t="inlineStr">
+        <is>
+          <t>85.275775</t>
+        </is>
+      </c>
+      <c r="AQ38" s="3" t="inlineStr"/>
+      <c r="AR38" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS38" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 22m</t>
+        </is>
+      </c>
+      <c r="AT38" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 22m</t>
+        </is>
+      </c>
+      <c r="AU38" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV38" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW38" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX38" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Oct_2026.xlsx
@@ -1117,7 +1117,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -7807,10 +7807,8 @@
           <t>Roman Shrestha</t>
         </is>
       </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t>9828559226</t>
-        </is>
+      <c r="O35" s="3" t="n">
+        <v>9828559226</v>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
@@ -7845,10 +7843,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y35" s="3" t="inlineStr">
-        <is>
-          <t>27.67445</t>
-        </is>
+      <c r="Y35" s="3" t="n">
+        <v>27.67445</v>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
@@ -7900,25 +7896,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN35" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN35" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO35" s="3" t="inlineStr">
         <is>
           <t>CDB635</t>
         </is>
       </c>
-      <c r="AP35" s="3" t="inlineStr">
-        <is>
-          <t>85.33265</t>
-        </is>
+      <c r="AP35" s="3" t="n">
+        <v>85.33265</v>
       </c>
       <c r="AQ35" s="3" t="inlineStr"/>
       <c r="AR35" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS35" s="3" t="inlineStr">
@@ -8019,10 +8011,8 @@
           <t>Suresh Kumar</t>
         </is>
       </c>
-      <c r="O36" s="3" t="inlineStr">
-        <is>
-          <t>9812886249</t>
-        </is>
+      <c r="O36" s="3" t="n">
+        <v>9812886249</v>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
@@ -8057,10 +8047,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y36" s="3" t="inlineStr">
-        <is>
-          <t>27.687738</t>
-        </is>
+      <c r="Y36" s="3" t="n">
+        <v>27.687738</v>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
@@ -8098,10 +8086,8 @@
           <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
-      <c r="AH36" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH36" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI36" s="3" t="inlineStr"/>
       <c r="AJ36" s="3" t="inlineStr"/>
@@ -8116,25 +8102,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN36" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN36" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
           <t>4,12</t>
         </is>
       </c>
-      <c r="AP36" s="3" t="inlineStr">
-        <is>
-          <t>85.297712</t>
-        </is>
+      <c r="AP36" s="3" t="n">
+        <v>85.297712</v>
       </c>
       <c r="AQ36" s="3" t="inlineStr"/>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv stb box faulty    has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
@@ -8235,10 +8217,8 @@
           <t>Keshab Rijal</t>
         </is>
       </c>
-      <c r="O37" s="3" t="inlineStr">
-        <is>
-          <t>9866316594</t>
-        </is>
+      <c r="O37" s="3" t="n">
+        <v>9866316594</v>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
@@ -8273,10 +8253,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y37" s="3" t="inlineStr">
-        <is>
-          <t>27.695898</t>
-        </is>
+      <c r="Y37" s="3" t="n">
+        <v>27.695898</v>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
@@ -8332,25 +8310,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN37" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN37" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
           <t>CDB218</t>
         </is>
       </c>
-      <c r="AP37" s="3" t="inlineStr">
-        <is>
-          <t>85.275775</t>
-        </is>
+      <c r="AP37" s="3" t="n">
+        <v>85.275775</v>
       </c>
       <c r="AQ37" s="3" t="inlineStr"/>
       <c r="AR37" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS37" s="3" t="inlineStr">
@@ -8451,10 +8425,8 @@
           <t>Keshab Rijal</t>
         </is>
       </c>
-      <c r="O38" s="3" t="inlineStr">
-        <is>
-          <t>9866316594</t>
-        </is>
+      <c r="O38" s="3" t="n">
+        <v>9866316594</v>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
@@ -8489,10 +8461,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y38" s="3" t="inlineStr">
-        <is>
-          <t>27.695898</t>
-        </is>
+      <c r="Y38" s="3" t="n">
+        <v>27.695898</v>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
@@ -8548,25 +8518,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN38" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN38" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO38" s="3" t="inlineStr">
         <is>
           <t>CDB218</t>
         </is>
       </c>
-      <c r="AP38" s="3" t="inlineStr">
-        <is>
-          <t>85.275775</t>
-        </is>
+      <c r="AP38" s="3" t="n">
+        <v>85.275775</v>
       </c>
       <c r="AQ38" s="3" t="inlineStr"/>
       <c r="AR38" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS38" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Oct_2026.xlsx
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>6</v>
-      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>87.5%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>71.1%</t>
         </is>
       </c>
     </row>
@@ -688,19 +688,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>78.6%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>36.8%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.2%</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>39.5%</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
         <v>6</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>1</v>
@@ -832,7 +832,7 @@
         <v>2</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
@@ -1048,7 +1048,7 @@
         <v>6</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>5</v>
@@ -1057,7 +1057,7 @@
         <v>6</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1071,7 +1071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX38"/>
+  <dimension ref="A1:AX39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1117,7 +1117,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -8566,6 +8566,214 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 1:49 PM</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr"/>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379326</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>Kushal Gurung</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>Kushal Gurung</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t>9846316207</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr"/>
+      <c r="R39" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 01:49:49 PM</t>
+        </is>
+      </c>
+      <c r="S39" s="3" t="inlineStr"/>
+      <c r="T39" s="3" t="inlineStr"/>
+      <c r="U39" s="3" t="inlineStr">
+        <is>
+          <t>KLK9846316207</t>
+        </is>
+      </c>
+      <c r="V39" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 03:42:50 PM</t>
+        </is>
+      </c>
+      <c r="W39" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 01:49:49 PM</t>
+        </is>
+      </c>
+      <c r="X39" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y39" s="3" t="inlineStr"/>
+      <c r="Z39" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA39" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB39" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC39" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD39" s="3" t="inlineStr"/>
+      <c r="AE39" s="3" t="inlineStr">
+        <is>
+          <t>Townplanning samakhushi - Family restaurant P8J8+4C8 Samakhusi Marg 26 Kathmandu 44600, Bagmati, Nep</t>
+        </is>
+      </c>
+      <c r="AF39" s="3" t="inlineStr">
+        <is>
+          <t>9846316207@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG39" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH39" s="3" t="inlineStr"/>
+      <c r="AI39" s="3" t="inlineStr">
+        <is>
+          <t>04:07 hour</t>
+        </is>
+      </c>
+      <c r="AJ39" s="3" t="inlineStr"/>
+      <c r="AK39" s="3" t="inlineStr"/>
+      <c r="AL39" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM39" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN39" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO39" s="3" t="inlineStr">
+        <is>
+          <t>3,14</t>
+        </is>
+      </c>
+      <c r="AP39" s="3" t="inlineStr"/>
+      <c r="AQ39" s="3" t="inlineStr"/>
+      <c r="AR39" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS39" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT39" s="3" t="inlineStr">
+        <is>
+          <t>2d 22h 6m</t>
+        </is>
+      </c>
+      <c r="AU39" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV39" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW39" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX39" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Oct_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>6</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>87.5%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>71.1%</t>
+          <t>71.8%</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>35.9%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>12.8%</t>
         </is>
       </c>
     </row>
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>14</v>
-      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>93.3%</t>
+          <t>93.8%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>41.0%</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>6</v>
@@ -832,7 +832,7 @@
         <v>2</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
@@ -1045,7 +1045,7 @@
         <v>8</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D11" s="4" t="n">
         <v>7</v>
@@ -1057,7 +1057,7 @@
         <v>6</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1071,7 +1071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX39"/>
+  <dimension ref="A1:AX40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -8633,10 +8633,8 @@
           <t>Kushal Gurung</t>
         </is>
       </c>
-      <c r="O39" s="3" t="inlineStr">
-        <is>
-          <t>9846316207</t>
-        </is>
+      <c r="O39" s="3" t="n">
+        <v>9846316207</v>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
@@ -8726,10 +8724,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN39" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN39" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO39" s="3" t="inlineStr">
         <is>
@@ -8740,37 +8736,253 @@
       <c r="AQ39" s="3" t="inlineStr"/>
       <c r="AR39" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS39" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT39" s="3" t="inlineStr">
+        <is>
+          <t>2d 22h 6m</t>
+        </is>
+      </c>
+      <c r="AU39" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV39" s="3" t="inlineStr">
+        <is>
           <t>Case : Router Upgrade  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS39" s="3" t="inlineStr">
+      <c r="AW39" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX39" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 2:03 PM</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr"/>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379893</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>Devi Raman Adhikari</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t>Devi Raman Adhikari</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t>9801202412</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr"/>
+      <c r="R40" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 02:03:28 PM</t>
+        </is>
+      </c>
+      <c r="S40" s="3" t="inlineStr"/>
+      <c r="T40" s="3" t="inlineStr"/>
+      <c r="U40" s="3" t="inlineStr">
+        <is>
+          <t>9801202412</t>
+        </is>
+      </c>
+      <c r="V40" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 09:03:20 AM</t>
+        </is>
+      </c>
+      <c r="W40" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 02:03:28 PM</t>
+        </is>
+      </c>
+      <c r="X40" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y40" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA40" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB40" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC40" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD40" s="3" t="inlineStr"/>
+      <c r="AE40" s="3" t="inlineStr">
+        <is>
+          <t>Near Srijanshil Boarding School, Madan Bhandari Path, Basanta Marg, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF40" s="3" t="inlineStr">
+        <is>
+          <t>deviradhikaricmc@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG40" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH40" s="3" t="inlineStr"/>
+      <c r="AI40" s="3" t="inlineStr">
+        <is>
+          <t>00:03 hour</t>
+        </is>
+      </c>
+      <c r="AJ40" s="3" t="inlineStr"/>
+      <c r="AK40" s="3" t="inlineStr"/>
+      <c r="AL40" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Yonjan</t>
+        </is>
+      </c>
+      <c r="AM40" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN40" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO40" s="3" t="inlineStr">
+        <is>
+          <t>CDB342</t>
+        </is>
+      </c>
+      <c r="AP40" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ40" s="3" t="inlineStr"/>
+      <c r="AR40" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS40" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT39" s="3" t="inlineStr">
-        <is>
-          <t>2d 22h 6m</t>
-        </is>
-      </c>
-      <c r="AU39" s="3" t="inlineStr">
+      <c r="AT40" s="3" t="inlineStr">
+        <is>
+          <t>2d 5h</t>
+        </is>
+      </c>
+      <c r="AU40" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV39" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router Upgrade  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="AW39" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="AX39" s="3" t="inlineStr">
-        <is>
-          <t>Sanjeev Giri</t>
+      <c r="AV40" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW40" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX40" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Oct_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>7</v>
-      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>71.8%</t>
+          <t>72.7%</t>
         </is>
       </c>
     </row>
@@ -688,19 +688,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>11</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>73.3%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>34.1%</t>
         </is>
       </c>
     </row>
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>13.6%</t>
         </is>
       </c>
     </row>
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>93.8%</t>
+          <t>94.7%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>41.0%</t>
+          <t>43.2%</t>
         </is>
       </c>
     </row>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>7</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>1</v>
@@ -832,7 +832,7 @@
         <v>2</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -848,7 +848,7 @@
         <v>0</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>1</v>
@@ -857,7 +857,7 @@
         <v>2</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -888,11 +888,11 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>ONT and Setup Box Recovery</t>
+          <t>IPTV STB Adaptor damage Issue</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0</v>
@@ -901,19 +901,19 @@
         <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="G5" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB Adaptor damage Issue</t>
+          <t>ONT and Setup Box Recovery</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -926,10 +926,10 @@
         <v>0</v>
       </c>
       <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>1</v>
@@ -1042,13 +1042,13 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>7</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>5</v>
@@ -1057,7 +1057,7 @@
         <v>6</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1071,7 +1071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX40"/>
+  <dimension ref="A1:AX45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -8837,10 +8837,8 @@
           <t>Devi Raman Adhikari</t>
         </is>
       </c>
-      <c r="O40" s="3" t="inlineStr">
-        <is>
-          <t>9801202412</t>
-        </is>
+      <c r="O40" s="3" t="n">
+        <v>9801202412</v>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
@@ -8875,10 +8873,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y40" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y40" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
@@ -8934,55 +8930,1115 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN40" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN40" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO40" s="3" t="inlineStr">
         <is>
           <t>CDB342</t>
         </is>
       </c>
-      <c r="AP40" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP40" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ40" s="3" t="inlineStr"/>
       <c r="AR40" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS40" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT40" s="3" t="inlineStr">
+        <is>
+          <t>2d 5h</t>
+        </is>
+      </c>
+      <c r="AU40" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV40" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS40" s="3" t="inlineStr">
+      <c r="AW40" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX40" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 2:21 PM</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr"/>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379348</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>Shashi Shrestha</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>Shashi Shrestha</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t>9813316947</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q41" s="3" t="inlineStr"/>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 02:21:24 PM</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="inlineStr"/>
+      <c r="T41" s="3" t="inlineStr"/>
+      <c r="U41" s="3" t="inlineStr">
+        <is>
+          <t>9813316947</t>
+        </is>
+      </c>
+      <c r="V41" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 04:02:47 PM</t>
+        </is>
+      </c>
+      <c r="W41" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 02:21:24 PM</t>
+        </is>
+      </c>
+      <c r="X41" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y41" s="3" t="inlineStr">
+        <is>
+          <t>27.73944</t>
+        </is>
+      </c>
+      <c r="Z41" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA41" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB41" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC41" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD41" s="3" t="inlineStr"/>
+      <c r="AE41" s="3" t="inlineStr">
+        <is>
+          <t>Mitho Sagun Sarbottam Pitho Udhyog, Balaju, Kathmandu , Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF41" s="3" t="inlineStr">
+        <is>
+          <t>sasialex21@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG41" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH41" s="3" t="inlineStr"/>
+      <c r="AI41" s="3" t="inlineStr">
+        <is>
+          <t>04:19 hour</t>
+        </is>
+      </c>
+      <c r="AJ41" s="3" t="inlineStr"/>
+      <c r="AK41" s="3" t="inlineStr"/>
+      <c r="AL41" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM41" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN41" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO41" s="3" t="inlineStr">
+        <is>
+          <t>CDB071</t>
+        </is>
+      </c>
+      <c r="AP41" s="3" t="inlineStr">
+        <is>
+          <t>85.30056</t>
+        </is>
+      </c>
+      <c r="AQ41" s="3" t="inlineStr"/>
+      <c r="AR41" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS41" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT40" s="3" t="inlineStr">
-        <is>
-          <t>2d 5h</t>
-        </is>
-      </c>
-      <c r="AU40" s="3" t="inlineStr">
+      <c r="AT41" s="3" t="inlineStr">
+        <is>
+          <t>2d 22h 18m</t>
+        </is>
+      </c>
+      <c r="AU41" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV40" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="AW40" s="3" t="inlineStr">
+      <c r="AV41" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW41" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX40" s="3" t="inlineStr">
-        <is>
-          <t>Rajesh Maharjan</t>
+      <c r="AX41" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 2:20 PM</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr"/>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>no light issue</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379334</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>Debraj Sapkota</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t>Debraj Sapkota</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t>9841524284</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="inlineStr"/>
+      <c r="R42" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 02:20:49 PM</t>
+        </is>
+      </c>
+      <c r="S42" s="3" t="inlineStr"/>
+      <c r="T42" s="3" t="inlineStr"/>
+      <c r="U42" s="3" t="inlineStr">
+        <is>
+          <t>9841524284</t>
+        </is>
+      </c>
+      <c r="V42" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 03:48:09 PM</t>
+        </is>
+      </c>
+      <c r="W42" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 02:20:49 PM</t>
+        </is>
+      </c>
+      <c r="X42" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y42" s="3" t="inlineStr">
+        <is>
+          <t>27.72891</t>
+        </is>
+      </c>
+      <c r="Z42" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA42" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB42" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC42" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD42" s="3" t="inlineStr"/>
+      <c r="AE42" s="3" t="inlineStr">
+        <is>
+          <t>Behind SEB School, Susangam Street, Samakhusi - Behind SEB School, Susangam Street", Bagmati, Centra</t>
+        </is>
+      </c>
+      <c r="AF42" s="3" t="inlineStr">
+        <is>
+          <t>debrajsapkota10@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG42" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH42" s="3" t="inlineStr"/>
+      <c r="AI42" s="3" t="inlineStr"/>
+      <c r="AJ42" s="3" t="inlineStr"/>
+      <c r="AK42" s="3" t="inlineStr"/>
+      <c r="AL42" s="3" t="inlineStr">
+        <is>
+          <t>Ayush Basnet</t>
+        </is>
+      </c>
+      <c r="AM42" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN42" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO42" s="3" t="inlineStr">
+        <is>
+          <t>L25-1</t>
+        </is>
+      </c>
+      <c r="AP42" s="3" t="inlineStr">
+        <is>
+          <t>85.31345</t>
+        </is>
+      </c>
+      <c r="AQ42" s="3" t="inlineStr"/>
+      <c r="AR42" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS42" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT42" s="3" t="inlineStr">
+        <is>
+          <t>2d 22h 32m</t>
+        </is>
+      </c>
+      <c r="AU42" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV42" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW42" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX42" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 2:20 PM</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>TKT1380419</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>Sachyut Vaidya</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>Sachyut Vaidya</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t>9866277798</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr"/>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 02:20:50 PM</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr"/>
+      <c r="T43" s="3" t="inlineStr"/>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t>9841406619</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 03:24:40 PM</t>
+        </is>
+      </c>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 02:20:50 PM</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y43" s="3" t="inlineStr">
+        <is>
+          <t>27.68521</t>
+        </is>
+      </c>
+      <c r="Z43" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA43" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB43" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC43" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD43" s="3" t="inlineStr"/>
+      <c r="AE43" s="3" t="inlineStr">
+        <is>
+          <t>Next to Prabhu Bank ATM,Balkhu,Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF43" s="3" t="inlineStr"/>
+      <c r="AG43" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH43" s="3" t="inlineStr"/>
+      <c r="AI43" s="3" t="inlineStr">
+        <is>
+          <t>18:56 hour</t>
+        </is>
+      </c>
+      <c r="AJ43" s="3" t="inlineStr"/>
+      <c r="AK43" s="3" t="inlineStr"/>
+      <c r="AL43" s="3" t="inlineStr">
+        <is>
+          <t>Joshna Shrestha</t>
+        </is>
+      </c>
+      <c r="AM43" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN43" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO43" s="3" t="inlineStr">
+        <is>
+          <t>3,5</t>
+        </is>
+      </c>
+      <c r="AP43" s="3" t="inlineStr">
+        <is>
+          <t>85.2973</t>
+        </is>
+      </c>
+      <c r="AQ43" s="3" t="inlineStr"/>
+      <c r="AR43" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS43" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT43" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 56m</t>
+        </is>
+      </c>
+      <c r="AU43" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV43" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW43" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX43" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 2:19 PM</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>TKT1380060</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>Ganesh Thapa</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t>Ganesh Thapa</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="inlineStr">
+        <is>
+          <t>9843840100</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q44" s="3" t="inlineStr"/>
+      <c r="R44" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 02:19:49 PM</t>
+        </is>
+      </c>
+      <c r="S44" s="3" t="inlineStr"/>
+      <c r="T44" s="3" t="inlineStr"/>
+      <c r="U44" s="3" t="inlineStr">
+        <is>
+          <t>9843840100</t>
+        </is>
+      </c>
+      <c r="V44" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 11:11:48 AM</t>
+        </is>
+      </c>
+      <c r="W44" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 02:19:49 PM</t>
+        </is>
+      </c>
+      <c r="X44" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y44" s="3" t="inlineStr"/>
+      <c r="Z44" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA44" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB44" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC44" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD44" s="3" t="inlineStr"/>
+      <c r="AE44" s="3" t="inlineStr">
+        <is>
+          <t>Nepal Bible Society - Religious organization M892+243 Bagdol Rd Lalitpur , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF44" s="3" t="inlineStr">
+        <is>
+          <t>kaalvairab666@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG44" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH44" s="3" t="inlineStr"/>
+      <c r="AI44" s="3" t="inlineStr">
+        <is>
+          <t>23:08 hour</t>
+        </is>
+      </c>
+      <c r="AJ44" s="3" t="inlineStr"/>
+      <c r="AK44" s="3" t="inlineStr"/>
+      <c r="AL44" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM44" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN44" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO44" s="3" t="inlineStr">
+        <is>
+          <t>3,15</t>
+        </is>
+      </c>
+      <c r="AP44" s="3" t="inlineStr"/>
+      <c r="AQ44" s="3" t="inlineStr"/>
+      <c r="AR44" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS44" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT44" s="3" t="inlineStr">
+        <is>
+          <t>2d 3h 8m</t>
+        </is>
+      </c>
+      <c r="AU44" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV44" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW44" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX44" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 2:18 PM</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>IPTV ISSUE</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379585</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>Birendra Kumar Chaudhary</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>Birendra Kumar Chaudhary</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t>9841142956</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q45" s="3" t="inlineStr"/>
+      <c r="R45" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 02:18:56 PM</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="inlineStr"/>
+      <c r="T45" s="3" t="inlineStr"/>
+      <c r="U45" s="3" t="inlineStr">
+        <is>
+          <t>9841142956</t>
+        </is>
+      </c>
+      <c r="V45" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 06:34:14 PM</t>
+        </is>
+      </c>
+      <c r="W45" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 02:18:56 PM</t>
+        </is>
+      </c>
+      <c r="X45" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y45" s="3" t="inlineStr">
+        <is>
+          <t>27.673707</t>
+        </is>
+      </c>
+      <c r="Z45" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA45" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB45" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC45" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD45" s="3" t="inlineStr"/>
+      <c r="AE45" s="3" t="inlineStr">
+        <is>
+          <t>M7CW+W6C, Malpokhari Marg, Lalitpur 44700 near Malpokhari Field, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF45" s="3" t="inlineStr">
+        <is>
+          <t>birendratharu1456@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG45" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH45" s="3" t="inlineStr"/>
+      <c r="AI45" s="3" t="inlineStr">
+        <is>
+          <t>01:44 hour</t>
+        </is>
+      </c>
+      <c r="AJ45" s="3" t="inlineStr"/>
+      <c r="AK45" s="3" t="inlineStr"/>
+      <c r="AL45" s="3" t="inlineStr">
+        <is>
+          <t>Sitaram Adhikari</t>
+        </is>
+      </c>
+      <c r="AM45" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN45" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO45" s="3" t="inlineStr">
+        <is>
+          <t>1,11</t>
+        </is>
+      </c>
+      <c r="AP45" s="3" t="inlineStr">
+        <is>
+          <t>85.300708</t>
+        </is>
+      </c>
+      <c r="AQ45" s="3" t="inlineStr"/>
+      <c r="AR45" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS45" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT45" s="3" t="inlineStr">
+        <is>
+          <t>2d 19h 44m</t>
+        </is>
+      </c>
+      <c r="AU45" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV45" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW45" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX45" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Oct_2026.xlsx
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>77.8%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>73.3%</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>15.6%</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>42.2%</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB Adaptor damage Issue</t>
+          <t>Replace SKYCOM to NETTV</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -901,10 +901,10 @@
         <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>2</v>
@@ -913,11 +913,11 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>ONT and Setup Box Recovery</t>
+          <t>IPTV STB Adaptor damage Issue</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0</v>
@@ -926,13 +926,13 @@
         <v>0</v>
       </c>
       <c r="E6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="G6" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -963,7 +963,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Query For Secondary Router /Repeater</t>
+          <t>ONT and Setup Box Recovery</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
@@ -973,13 +973,13 @@
         <v>0</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>1</v>
@@ -988,17 +988,17 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Replace SKYCOM to NETTV</t>
+          <t>Query For Secondary Router /Repeater</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>0</v>
@@ -1054,10 +1054,10 @@
         <v>5</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1071,7 +1071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX45"/>
+  <dimension ref="A1:AX46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -9035,20 +9035,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M41" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M41" s="3" t="inlineStr"/>
       <c r="N41" s="3" t="inlineStr">
         <is>
           <t>Shashi Shrestha</t>
         </is>
       </c>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
-          <t>9813316947</t>
-        </is>
+      <c r="O41" s="3" t="n">
+        <v>9813316947</v>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
@@ -9083,10 +9077,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y41" s="3" t="inlineStr">
-        <is>
-          <t>27.73944</t>
-        </is>
+      <c r="Y41" s="3" t="n">
+        <v>27.73944</v>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
@@ -9142,25 +9134,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN41" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN41" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO41" s="3" t="inlineStr">
         <is>
           <t>CDB071</t>
         </is>
       </c>
-      <c r="AP41" s="3" t="inlineStr">
-        <is>
-          <t>85.30056</t>
-        </is>
+      <c r="AP41" s="3" t="n">
+        <v>85.30056</v>
       </c>
       <c r="AQ41" s="3" t="inlineStr"/>
       <c r="AR41" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS41" s="3" t="inlineStr">
@@ -9261,10 +9249,8 @@
           <t>Debraj Sapkota</t>
         </is>
       </c>
-      <c r="O42" s="3" t="inlineStr">
-        <is>
-          <t>9841524284</t>
-        </is>
+      <c r="O42" s="3" t="n">
+        <v>9841524284</v>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
@@ -9299,10 +9285,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y42" s="3" t="inlineStr">
-        <is>
-          <t>27.72891</t>
-        </is>
+      <c r="Y42" s="3" t="n">
+        <v>27.72891</v>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
@@ -9354,25 +9338,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN42" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN42" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO42" s="3" t="inlineStr">
         <is>
           <t>L25-1</t>
         </is>
       </c>
-      <c r="AP42" s="3" t="inlineStr">
-        <is>
-          <t>85.31345</t>
-        </is>
+      <c r="AP42" s="3" t="n">
+        <v>85.31345</v>
       </c>
       <c r="AQ42" s="3" t="inlineStr"/>
       <c r="AR42" s="3" t="inlineStr">
         <is>
-          <t>Case : no light issue  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS42" s="3" t="inlineStr">
@@ -9473,10 +9453,8 @@
           <t>Sachyut Vaidya</t>
         </is>
       </c>
-      <c r="O43" s="3" t="inlineStr">
-        <is>
-          <t>9866277798</t>
-        </is>
+      <c r="O43" s="3" t="n">
+        <v>9866277798</v>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
@@ -9511,10 +9489,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y43" s="3" t="inlineStr">
-        <is>
-          <t>27.68521</t>
-        </is>
+      <c r="Y43" s="3" t="n">
+        <v>27.68521</v>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
@@ -9566,25 +9542,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN43" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN43" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO43" s="3" t="inlineStr">
         <is>
           <t>3,5</t>
         </is>
       </c>
-      <c r="AP43" s="3" t="inlineStr">
-        <is>
-          <t>85.2973</t>
-        </is>
+      <c r="AP43" s="3" t="n">
+        <v>85.29730000000001</v>
       </c>
       <c r="AQ43" s="3" t="inlineStr"/>
       <c r="AR43" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS43" s="3" t="inlineStr">
@@ -9685,10 +9657,8 @@
           <t>Ganesh Thapa</t>
         </is>
       </c>
-      <c r="O44" s="3" t="inlineStr">
-        <is>
-          <t>9843840100</t>
-        </is>
+      <c r="O44" s="3" t="n">
+        <v>9843840100</v>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
@@ -9778,10 +9748,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN44" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN44" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO44" s="3" t="inlineStr">
         <is>
@@ -9792,7 +9760,7 @@
       <c r="AQ44" s="3" t="inlineStr"/>
       <c r="AR44" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS44" s="3" t="inlineStr">
@@ -9893,10 +9861,8 @@
           <t>Birendra Kumar Chaudhary</t>
         </is>
       </c>
-      <c r="O45" s="3" t="inlineStr">
-        <is>
-          <t>9841142956</t>
-        </is>
+      <c r="O45" s="3" t="n">
+        <v>9841142956</v>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
@@ -9931,10 +9897,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y45" s="3" t="inlineStr">
-        <is>
-          <t>27.673707</t>
-        </is>
+      <c r="Y45" s="3" t="n">
+        <v>27.673707</v>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
@@ -9990,47 +9954,43 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN45" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN45" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO45" s="3" t="inlineStr">
         <is>
           <t>1,11</t>
         </is>
       </c>
-      <c r="AP45" s="3" t="inlineStr">
-        <is>
-          <t>85.300708</t>
-        </is>
+      <c r="AP45" s="3" t="n">
+        <v>85.300708</v>
       </c>
       <c r="AQ45" s="3" t="inlineStr"/>
       <c r="AR45" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS45" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT45" s="3" t="inlineStr">
+        <is>
+          <t>2d 19h 44m</t>
+        </is>
+      </c>
+      <c r="AU45" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV45" s="3" t="inlineStr">
+        <is>
           <t>Case : IPTV ISSUE  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS45" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT45" s="3" t="inlineStr">
-        <is>
-          <t>2d 19h 44m</t>
-        </is>
-      </c>
-      <c r="AU45" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV45" s="3" t="inlineStr">
-        <is>
-          <t>Case : IPTV ISSUE  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
       <c r="AW45" s="3" t="inlineStr">
         <is>
           <t>IPTV Issue</t>
@@ -10039,6 +9999,222 @@
       <c r="AX45" s="3" t="inlineStr">
         <is>
           <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 2:42 PM</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr"/>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>Case : Setup box connection  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>Setup box connection</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379446</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>Dipesh Nakarmi</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>Dipesh Nakarmi</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t>9863227220</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr"/>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 06:10:21 PM</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr"/>
+      <c r="T46" s="3" t="inlineStr"/>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t>KLK9863227220</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 04:53:20 PM</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 02:42:22 PM</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y46" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z46" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA46" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB46" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC46" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD46" s="3" t="inlineStr"/>
+      <c r="AE46" s="3" t="inlineStr">
+        <is>
+          <t>27.668180453495612, 85.26695337705654, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF46" s="3" t="inlineStr">
+        <is>
+          <t>dipeshnakarmi3@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG46" s="3" t="inlineStr">
+        <is>
+          <t>Replace SKYCOM to NETTV</t>
+        </is>
+      </c>
+      <c r="AH46" s="3" t="inlineStr"/>
+      <c r="AI46" s="3" t="inlineStr">
+        <is>
+          <t>03:49 hour</t>
+        </is>
+      </c>
+      <c r="AJ46" s="3" t="inlineStr"/>
+      <c r="AK46" s="3" t="inlineStr"/>
+      <c r="AL46" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM46" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN46" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO46" s="3" t="inlineStr">
+        <is>
+          <t>A03-CDB5</t>
+        </is>
+      </c>
+      <c r="AP46" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ46" s="3" t="inlineStr"/>
+      <c r="AR46" s="3" t="inlineStr">
+        <is>
+          <t>Case : Setup box connection  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS46" s="3" t="inlineStr">
+        <is>
+          <t>1d 20h 32m</t>
+        </is>
+      </c>
+      <c r="AT46" s="3" t="inlineStr">
+        <is>
+          <t>2d 21h 49m</t>
+        </is>
+      </c>
+      <c r="AU46" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV46" s="3" t="inlineStr">
+        <is>
+          <t>Case : Setup box connection  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW46" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX46" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Oct_2026.xlsx
@@ -1117,7 +1117,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -10069,10 +10069,8 @@
           <t>Dipesh Nakarmi</t>
         </is>
       </c>
-      <c r="O46" s="3" t="inlineStr">
-        <is>
-          <t>9863227220</t>
-        </is>
+      <c r="O46" s="3" t="n">
+        <v>9863227220</v>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
@@ -10107,10 +10105,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y46" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y46" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
@@ -10166,25 +10162,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN46" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN46" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO46" s="3" t="inlineStr">
         <is>
           <t>A03-CDB5</t>
         </is>
       </c>
-      <c r="AP46" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP46" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ46" s="3" t="inlineStr"/>
       <c r="AR46" s="3" t="inlineStr">
         <is>
-          <t>Case : Setup box connection  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS46" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Oct_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>6</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>46.2%</t>
         </is>
       </c>
     </row>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>8</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>72.7%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>33</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>70.2%</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>31.9%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>14.9%</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>40.4%</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX46"/>
+  <dimension ref="A1:AX48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -10210,6 +10210,222 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 3:00 PM</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr"/>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Router Upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr"/>
+      <c r="J47" s="3" t="inlineStr"/>
+      <c r="K47" s="3" t="inlineStr"/>
+      <c r="L47" s="3" t="inlineStr"/>
+      <c r="M47" s="3" t="inlineStr"/>
+      <c r="N47" s="3" t="inlineStr"/>
+      <c r="O47" s="3" t="inlineStr"/>
+      <c r="P47" s="3" t="inlineStr"/>
+      <c r="Q47" s="3" t="inlineStr"/>
+      <c r="R47" s="3" t="inlineStr"/>
+      <c r="S47" s="3" t="inlineStr"/>
+      <c r="T47" s="3" t="inlineStr"/>
+      <c r="U47" s="3" t="inlineStr"/>
+      <c r="V47" s="3" t="inlineStr"/>
+      <c r="W47" s="3" t="inlineStr"/>
+      <c r="X47" s="3" t="inlineStr"/>
+      <c r="Y47" s="3" t="inlineStr"/>
+      <c r="Z47" s="3" t="inlineStr"/>
+      <c r="AA47" s="3" t="inlineStr"/>
+      <c r="AB47" s="3" t="inlineStr"/>
+      <c r="AC47" s="3" t="inlineStr"/>
+      <c r="AD47" s="3" t="inlineStr"/>
+      <c r="AE47" s="3" t="inlineStr"/>
+      <c r="AF47" s="3" t="inlineStr"/>
+      <c r="AG47" s="3" t="inlineStr"/>
+      <c r="AH47" s="3" t="inlineStr"/>
+      <c r="AI47" s="3" t="inlineStr"/>
+      <c r="AJ47" s="3" t="inlineStr"/>
+      <c r="AK47" s="3" t="inlineStr"/>
+      <c r="AL47" s="3" t="inlineStr"/>
+      <c r="AM47" s="3" t="inlineStr"/>
+      <c r="AN47" s="3" t="inlineStr"/>
+      <c r="AO47" s="3" t="inlineStr"/>
+      <c r="AP47" s="3" t="inlineStr"/>
+      <c r="AQ47" s="3" t="inlineStr"/>
+      <c r="AR47" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS47" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT47" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU47" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV47" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Router Upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW47" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX47" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 3:16 PM</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr"/>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv setbox issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr"/>
+      <c r="J48" s="3" t="inlineStr"/>
+      <c r="K48" s="3" t="inlineStr"/>
+      <c r="L48" s="3" t="inlineStr"/>
+      <c r="M48" s="3" t="inlineStr"/>
+      <c r="N48" s="3" t="inlineStr"/>
+      <c r="O48" s="3" t="inlineStr"/>
+      <c r="P48" s="3" t="inlineStr"/>
+      <c r="Q48" s="3" t="inlineStr"/>
+      <c r="R48" s="3" t="inlineStr"/>
+      <c r="S48" s="3" t="inlineStr"/>
+      <c r="T48" s="3" t="inlineStr"/>
+      <c r="U48" s="3" t="inlineStr"/>
+      <c r="V48" s="3" t="inlineStr"/>
+      <c r="W48" s="3" t="inlineStr"/>
+      <c r="X48" s="3" t="inlineStr"/>
+      <c r="Y48" s="3" t="inlineStr"/>
+      <c r="Z48" s="3" t="inlineStr"/>
+      <c r="AA48" s="3" t="inlineStr"/>
+      <c r="AB48" s="3" t="inlineStr"/>
+      <c r="AC48" s="3" t="inlineStr"/>
+      <c r="AD48" s="3" t="inlineStr"/>
+      <c r="AE48" s="3" t="inlineStr"/>
+      <c r="AF48" s="3" t="inlineStr"/>
+      <c r="AG48" s="3" t="inlineStr"/>
+      <c r="AH48" s="3" t="inlineStr"/>
+      <c r="AI48" s="3" t="inlineStr"/>
+      <c r="AJ48" s="3" t="inlineStr"/>
+      <c r="AK48" s="3" t="inlineStr"/>
+      <c r="AL48" s="3" t="inlineStr"/>
+      <c r="AM48" s="3" t="inlineStr"/>
+      <c r="AN48" s="3" t="inlineStr"/>
+      <c r="AO48" s="3" t="inlineStr"/>
+      <c r="AP48" s="3" t="inlineStr"/>
+      <c r="AQ48" s="3" t="inlineStr"/>
+      <c r="AR48" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS48" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT48" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU48" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV48" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv setbox issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW48" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX48" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Oct_2026.xlsx
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>5</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>33</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>70.2%</t>
+          <t>68.8%</t>
         </is>
       </c>
     </row>
@@ -688,19 +688,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>11</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>14.6%</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>39.6%</t>
         </is>
       </c>
     </row>
@@ -826,13 +826,13 @@
         <v>7</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -1051,13 +1051,13 @@
         <v>9</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F11" s="4" t="n">
         <v>7</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1071,7 +1071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX48"/>
+  <dimension ref="A1:AX49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1117,7 +1117,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -10426,6 +10426,218 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 3:45 PM</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr"/>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>Case : stb collection  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>stb collection</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>TKT1376366</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>Dil Bahadur Shrestha</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
+          <t>Dil Bahadur Shrestha</t>
+        </is>
+      </c>
+      <c r="O49" s="3" t="inlineStr">
+        <is>
+          <t>9841497101</t>
+        </is>
+      </c>
+      <c r="P49" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q49" s="3" t="inlineStr"/>
+      <c r="R49" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 02:47:02 PM</t>
+        </is>
+      </c>
+      <c r="S49" s="3" t="inlineStr"/>
+      <c r="T49" s="3" t="inlineStr"/>
+      <c r="U49" s="3" t="inlineStr">
+        <is>
+          <t>9841497101</t>
+        </is>
+      </c>
+      <c r="V49" s="3" t="inlineStr">
+        <is>
+          <t>22 Oct 2026 08:58:40 PM</t>
+        </is>
+      </c>
+      <c r="W49" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 03:45:27 PM</t>
+        </is>
+      </c>
+      <c r="X49" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y49" s="3" t="inlineStr">
+        <is>
+          <t>27.64958</t>
+        </is>
+      </c>
+      <c r="Z49" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA49" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-CG Group</t>
+        </is>
+      </c>
+      <c r="AB49" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC49" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD49" s="3" t="inlineStr"/>
+      <c r="AE49" s="3" t="inlineStr">
+        <is>
+          <t>Imadol, Mahalaxmi-4, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF49" s="3" t="inlineStr">
+        <is>
+          <t>dilbdr123@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG49" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH49" s="3" t="inlineStr"/>
+      <c r="AI49" s="3" t="inlineStr"/>
+      <c r="AJ49" s="3" t="inlineStr"/>
+      <c r="AK49" s="3" t="inlineStr"/>
+      <c r="AL49" s="3" t="inlineStr">
+        <is>
+          <t>Pradeep Yadav</t>
+        </is>
+      </c>
+      <c r="AM49" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN49" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO49" s="3" t="inlineStr">
+        <is>
+          <t>L49-7</t>
+        </is>
+      </c>
+      <c r="AP49" s="3" t="inlineStr">
+        <is>
+          <t>85.34428</t>
+        </is>
+      </c>
+      <c r="AQ49" s="3" t="inlineStr"/>
+      <c r="AR49" s="3" t="inlineStr">
+        <is>
+          <t>Case : stb collection  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS49" s="3" t="inlineStr">
+        <is>
+          <t>2d 58m</t>
+        </is>
+      </c>
+      <c r="AT49" s="3" t="inlineStr">
+        <is>
+          <t>6d 18h 46m</t>
+        </is>
+      </c>
+      <c r="AU49" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV49" s="3" t="inlineStr">
+        <is>
+          <t>Case : stb collection  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW49" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX49" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Oct_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>69.4%</t>
         </is>
       </c>
     </row>
@@ -688,19 +688,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>70.6%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>34.7%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>38.8%</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX49"/>
+  <dimension ref="A1:AX50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -10483,20 +10483,14 @@
           <t>On Hold</t>
         </is>
       </c>
-      <c r="M49" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M49" s="3" t="inlineStr"/>
       <c r="N49" s="3" t="inlineStr">
         <is>
           <t>Dil Bahadur Shrestha</t>
         </is>
       </c>
-      <c r="O49" s="3" t="inlineStr">
-        <is>
-          <t>9841497101</t>
-        </is>
+      <c r="O49" s="3" t="n">
+        <v>9841497101</v>
       </c>
       <c r="P49" s="3" t="inlineStr">
         <is>
@@ -10531,10 +10525,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y49" s="3" t="inlineStr">
-        <is>
-          <t>27.64958</t>
-        </is>
+      <c r="Y49" s="3" t="n">
+        <v>27.64958</v>
       </c>
       <c r="Z49" s="3" t="inlineStr">
         <is>
@@ -10586,47 +10578,43 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN49" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN49" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO49" s="3" t="inlineStr">
         <is>
           <t>L49-7</t>
         </is>
       </c>
-      <c r="AP49" s="3" t="inlineStr">
-        <is>
-          <t>85.34428</t>
-        </is>
+      <c r="AP49" s="3" t="n">
+        <v>85.34428</v>
       </c>
       <c r="AQ49" s="3" t="inlineStr"/>
       <c r="AR49" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS49" s="3" t="inlineStr">
+        <is>
+          <t>2d 58m</t>
+        </is>
+      </c>
+      <c r="AT49" s="3" t="inlineStr">
+        <is>
+          <t>6d 18h 46m</t>
+        </is>
+      </c>
+      <c r="AU49" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV49" s="3" t="inlineStr">
+        <is>
           <t>Case : stb collection  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS49" s="3" t="inlineStr">
-        <is>
-          <t>2d 58m</t>
-        </is>
-      </c>
-      <c r="AT49" s="3" t="inlineStr">
-        <is>
-          <t>6d 18h 46m</t>
-        </is>
-      </c>
-      <c r="AU49" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV49" s="3" t="inlineStr">
-        <is>
-          <t>Case : stb collection  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="AW49" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
@@ -10635,6 +10623,214 @@
       <c r="AX49" s="3" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 3:56 PM</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr"/>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>TKT1378084</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>Raunak Maskay</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
+          <t>Raunak Maskay</t>
+        </is>
+      </c>
+      <c r="O50" s="3" t="inlineStr">
+        <is>
+          <t>9841126820</t>
+        </is>
+      </c>
+      <c r="P50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q50" s="3" t="inlineStr"/>
+      <c r="R50" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 03:56:01 PM</t>
+        </is>
+      </c>
+      <c r="S50" s="3" t="inlineStr"/>
+      <c r="T50" s="3" t="inlineStr"/>
+      <c r="U50" s="3" t="inlineStr">
+        <is>
+          <t>CHB9841126820</t>
+        </is>
+      </c>
+      <c r="V50" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 02:05:16 PM</t>
+        </is>
+      </c>
+      <c r="W50" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 03:56:01 PM</t>
+        </is>
+      </c>
+      <c r="X50" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y50" s="3" t="inlineStr"/>
+      <c r="Z50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA50" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB50" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC50" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD50" s="3" t="inlineStr"/>
+      <c r="AE50" s="3" t="inlineStr">
+        <is>
+          <t>Bajaj Lainchaur (Star Auto Enterprises) Nagpokhari Marg, Kathmandu 44600, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF50" s="3" t="inlineStr">
+        <is>
+          <t>raunakmaskay@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG50" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH50" s="3" t="inlineStr"/>
+      <c r="AI50" s="3" t="inlineStr">
+        <is>
+          <t>11:56 hour</t>
+        </is>
+      </c>
+      <c r="AJ50" s="3" t="inlineStr"/>
+      <c r="AK50" s="3" t="inlineStr"/>
+      <c r="AL50" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM50" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN50" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO50" s="3" t="inlineStr">
+        <is>
+          <t>CDB011</t>
+        </is>
+      </c>
+      <c r="AP50" s="3" t="inlineStr"/>
+      <c r="AQ50" s="3" t="inlineStr"/>
+      <c r="AR50" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS50" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT50" s="3" t="inlineStr">
+        <is>
+          <t>4d 1h 50m</t>
+        </is>
+      </c>
+      <c r="AU50" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV50" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX50" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Oct_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>7</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>88.9%</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>69.4%</t>
+          <t>70.6%</t>
         </is>
       </c>
     </row>
@@ -688,19 +688,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>72.2%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>35.3%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>13.7%</t>
         </is>
       </c>
     </row>
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>18</v>
-      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>94.7%</t>
+          <t>95.0%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>39.2%</t>
         </is>
       </c>
     </row>
@@ -820,19 +820,19 @@
         <v>4</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>7</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
@@ -1045,19 +1045,19 @@
         <v>11</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F11" s="4" t="n">
         <v>7</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -1071,7 +1071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX50"/>
+  <dimension ref="A1:AX52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -10693,10 +10693,8 @@
           <t>Raunak Maskay</t>
         </is>
       </c>
-      <c r="O50" s="3" t="inlineStr">
-        <is>
-          <t>9841126820</t>
-        </is>
+      <c r="O50" s="3" t="n">
+        <v>9841126820</v>
       </c>
       <c r="P50" s="3" t="inlineStr">
         <is>
@@ -10786,10 +10784,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN50" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN50" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO50" s="3" t="inlineStr">
         <is>
@@ -10800,37 +10796,461 @@
       <c r="AQ50" s="3" t="inlineStr"/>
       <c r="AR50" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS50" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT50" s="3" t="inlineStr">
+        <is>
+          <t>4d 1h 50m</t>
+        </is>
+      </c>
+      <c r="AU50" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV50" s="3" t="inlineStr">
+        <is>
           <t>Case : Router Upgrade   has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS50" s="3" t="inlineStr">
+      <c r="AW50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX50" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 4:12 PM</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr"/>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>TKT1380392</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Patwari</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Patwari</t>
+        </is>
+      </c>
+      <c r="O51" s="3" t="inlineStr">
+        <is>
+          <t>9840091310</t>
+        </is>
+      </c>
+      <c r="P51" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q51" s="3" t="inlineStr"/>
+      <c r="R51" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 04:12:15 PM</t>
+        </is>
+      </c>
+      <c r="S51" s="3" t="inlineStr"/>
+      <c r="T51" s="3" t="inlineStr"/>
+      <c r="U51" s="3" t="inlineStr">
+        <is>
+          <t>LTP9840091310</t>
+        </is>
+      </c>
+      <c r="V51" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 03:06:35 PM</t>
+        </is>
+      </c>
+      <c r="W51" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 04:12:15 PM</t>
+        </is>
+      </c>
+      <c r="X51" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y51" s="3" t="inlineStr"/>
+      <c r="Z51" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA51" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB51" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC51" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD51" s="3" t="inlineStr"/>
+      <c r="AE51" s="3" t="inlineStr">
+        <is>
+          <t>imadol Kamalpokhari, Nepal Bank Limited - Lalitpur Metropolitan, Lalitpur, Bagmati, Nepal, Nepal, Ka</t>
+        </is>
+      </c>
+      <c r="AF51" s="3" t="inlineStr">
+        <is>
+          <t>9840091310@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG51" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH51" s="3" t="inlineStr"/>
+      <c r="AI51" s="3" t="inlineStr">
+        <is>
+          <t>21:06 hour</t>
+        </is>
+      </c>
+      <c r="AJ51" s="3" t="inlineStr"/>
+      <c r="AK51" s="3" t="inlineStr"/>
+      <c r="AL51" s="3" t="inlineStr">
+        <is>
+          <t>Praktisha Subedi</t>
+        </is>
+      </c>
+      <c r="AM51" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN51" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO51" s="3" t="inlineStr">
+        <is>
+          <t>L43-1</t>
+        </is>
+      </c>
+      <c r="AP51" s="3" t="inlineStr"/>
+      <c r="AQ51" s="3" t="inlineStr"/>
+      <c r="AR51" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS51" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT50" s="3" t="inlineStr">
-        <is>
-          <t>4d 1h 50m</t>
-        </is>
-      </c>
-      <c r="AU50" s="3" t="inlineStr">
+      <c r="AT51" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 5m</t>
+        </is>
+      </c>
+      <c r="AU51" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV50" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router Upgrade   has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="AW50" s="3" t="inlineStr">
+      <c r="AV51" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW51" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX51" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 4:14 PM</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr"/>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgarde   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>Router upgarde</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>TKT1381282</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>Suresh M Joshi</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
+          <t>Suresh M Joshi</t>
+        </is>
+      </c>
+      <c r="O52" s="3" t="inlineStr">
+        <is>
+          <t>9851032477</t>
+        </is>
+      </c>
+      <c r="P52" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="AX50" s="3" t="inlineStr">
-        <is>
-          <t>Chandramani Tharu</t>
+      <c r="Q52" s="3" t="inlineStr"/>
+      <c r="R52" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 04:14:45 PM</t>
+        </is>
+      </c>
+      <c r="S52" s="3" t="inlineStr"/>
+      <c r="T52" s="3" t="inlineStr"/>
+      <c r="U52" s="3" t="inlineStr">
+        <is>
+          <t>sureshjoshi</t>
+        </is>
+      </c>
+      <c r="V52" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 01:23:28 PM</t>
+        </is>
+      </c>
+      <c r="W52" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 04:14:45 PM</t>
+        </is>
+      </c>
+      <c r="X52" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y52" s="3" t="inlineStr">
+        <is>
+          <t>27.6731</t>
+        </is>
+      </c>
+      <c r="Z52" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA52" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB52" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC52" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD52" s="3" t="inlineStr"/>
+      <c r="AE52" s="3" t="inlineStr">
+        <is>
+          <t>Mangal Bazar trilingshwor mahadev, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF52" s="3" t="inlineStr">
+        <is>
+          <t>evyak.joshi@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG52" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH52" s="3" t="inlineStr"/>
+      <c r="AI52" s="3" t="inlineStr">
+        <is>
+          <t>12:51 hour</t>
+        </is>
+      </c>
+      <c r="AJ52" s="3" t="inlineStr"/>
+      <c r="AK52" s="3" t="inlineStr"/>
+      <c r="AL52" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM52" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN52" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO52" s="3" t="inlineStr">
+        <is>
+          <t>1,12</t>
+        </is>
+      </c>
+      <c r="AP52" s="3" t="inlineStr">
+        <is>
+          <t>85.32237</t>
+        </is>
+      </c>
+      <c r="AQ52" s="3" t="inlineStr"/>
+      <c r="AR52" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgarde   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS52" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT52" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 51m</t>
+        </is>
+      </c>
+      <c r="AU52" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV52" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgarde   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW52" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX52" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Oct_2026.xlsx
@@ -1117,7 +1117,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -10887,20 +10887,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M51" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M51" s="3" t="inlineStr"/>
       <c r="N51" s="3" t="inlineStr">
         <is>
           <t>Laxman Patwari</t>
         </is>
       </c>
-      <c r="O51" s="3" t="inlineStr">
-        <is>
-          <t>9840091310</t>
-        </is>
+      <c r="O51" s="3" t="n">
+        <v>9840091310</v>
       </c>
       <c r="P51" s="3" t="inlineStr">
         <is>
@@ -10990,10 +10984,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN51" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN51" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO51" s="3" t="inlineStr">
         <is>
@@ -11004,7 +10996,7 @@
       <c r="AQ51" s="3" t="inlineStr"/>
       <c r="AR51" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS51" s="3" t="inlineStr">
@@ -11105,10 +11097,8 @@
           <t>Suresh M Joshi</t>
         </is>
       </c>
-      <c r="O52" s="3" t="inlineStr">
-        <is>
-          <t>9851032477</t>
-        </is>
+      <c r="O52" s="3" t="n">
+        <v>9851032477</v>
       </c>
       <c r="P52" s="3" t="inlineStr">
         <is>
@@ -11143,10 +11133,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y52" s="3" t="inlineStr">
-        <is>
-          <t>27.6731</t>
-        </is>
+      <c r="Y52" s="3" t="n">
+        <v>27.6731</v>
       </c>
       <c r="Z52" s="3" t="inlineStr">
         <is>
@@ -11202,25 +11190,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN52" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN52" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO52" s="3" t="inlineStr">
         <is>
           <t>1,12</t>
         </is>
       </c>
-      <c r="AP52" s="3" t="inlineStr">
-        <is>
-          <t>85.32237</t>
-        </is>
+      <c r="AP52" s="3" t="n">
+        <v>85.32237000000001</v>
       </c>
       <c r="AQ52" s="3" t="inlineStr"/>
       <c r="AR52" s="3" t="inlineStr">
         <is>
-          <t>Case : Router upgarde   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS52" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Oct_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>8</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>90.0%</t>
         </is>
       </c>
     </row>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="C6" s="3" t="n">
-        <v>7</v>
-      </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>81.8%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>72.7%</t>
         </is>
       </c>
     </row>
@@ -688,19 +688,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>36.4%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>12.7%</t>
         </is>
       </c>
     </row>
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>95.0%</t>
+          <t>95.5%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
@@ -820,19 +820,19 @@
         <v>4</v>
       </c>
       <c r="C2" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="D2" s="3" t="n">
         <v>8</v>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>7</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>3</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
@@ -1045,19 +1045,19 @@
         <v>11</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>7</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1071,7 +1071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX52"/>
+  <dimension ref="A1:AX56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1082,7 +1082,7 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="42" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
@@ -1117,7 +1117,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -11238,6 +11238,854 @@
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 4:36 PM</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr"/>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>TKT1382320</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>Rajan Sharma</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
+          <t>Rajan Sharma</t>
+        </is>
+      </c>
+      <c r="O53" s="3" t="inlineStr">
+        <is>
+          <t>9819008606</t>
+        </is>
+      </c>
+      <c r="P53" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q53" s="3" t="inlineStr"/>
+      <c r="R53" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 04:36:03 PM</t>
+        </is>
+      </c>
+      <c r="S53" s="3" t="inlineStr"/>
+      <c r="T53" s="3" t="inlineStr"/>
+      <c r="U53" s="3" t="inlineStr">
+        <is>
+          <t>9819008606</t>
+        </is>
+      </c>
+      <c r="V53" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 10:03:31 AM</t>
+        </is>
+      </c>
+      <c r="W53" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 04:36:03 PM</t>
+        </is>
+      </c>
+      <c r="X53" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y53" s="3" t="inlineStr"/>
+      <c r="Z53" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA53" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB53" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC53" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD53" s="3" t="inlineStr"/>
+      <c r="AE53" s="3" t="inlineStr">
+        <is>
+          <t>Near Mantar P94C+MCP, Gothatar Marg, Kageshwori Manohara , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF53" s="3" t="inlineStr">
+        <is>
+          <t>sharmarajan973@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG53" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH53" s="3" t="inlineStr"/>
+      <c r="AI53" s="3" t="inlineStr">
+        <is>
+          <t>06:33 hour</t>
+        </is>
+      </c>
+      <c r="AJ53" s="3" t="inlineStr"/>
+      <c r="AK53" s="3" t="inlineStr"/>
+      <c r="AL53" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM53" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN53" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO53" s="3" t="inlineStr">
+        <is>
+          <t>L29-7</t>
+        </is>
+      </c>
+      <c r="AP53" s="3" t="inlineStr"/>
+      <c r="AQ53" s="3" t="inlineStr"/>
+      <c r="AR53" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS53" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT53" s="3" t="inlineStr">
+        <is>
+          <t>6h 32m</t>
+        </is>
+      </c>
+      <c r="AU53" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV53" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW53" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX53" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 4:44 PM</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr"/>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>TKT1380317</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>Brison Maharjan</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
+          <t>Brison Maharjan</t>
+        </is>
+      </c>
+      <c r="O54" s="3" t="inlineStr">
+        <is>
+          <t>9864156296</t>
+        </is>
+      </c>
+      <c r="P54" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q54" s="3" t="inlineStr"/>
+      <c r="R54" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 04:44:59 PM</t>
+        </is>
+      </c>
+      <c r="S54" s="3" t="inlineStr"/>
+      <c r="T54" s="3" t="inlineStr"/>
+      <c r="U54" s="3" t="inlineStr">
+        <is>
+          <t>9864156296</t>
+        </is>
+      </c>
+      <c r="V54" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 02:01:52 PM</t>
+        </is>
+      </c>
+      <c r="W54" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 04:44:59 PM</t>
+        </is>
+      </c>
+      <c r="X54" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y54" s="3" t="inlineStr"/>
+      <c r="Z54" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA54" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB54" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC54" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD54" s="3" t="inlineStr"/>
+      <c r="AE54" s="3" t="inlineStr">
+        <is>
+          <t>Lalitpur ward no 12, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF54" s="3" t="inlineStr">
+        <is>
+          <t>Brisonmhrz43@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG54" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH54" s="3" t="inlineStr"/>
+      <c r="AI54" s="3" t="inlineStr">
+        <is>
+          <t>22:43 hour</t>
+        </is>
+      </c>
+      <c r="AJ54" s="3" t="inlineStr"/>
+      <c r="AK54" s="3" t="inlineStr"/>
+      <c r="AL54" s="3" t="inlineStr">
+        <is>
+          <t>Praktisha Subedi</t>
+        </is>
+      </c>
+      <c r="AM54" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN54" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO54" s="3" t="inlineStr">
+        <is>
+          <t>3,13</t>
+        </is>
+      </c>
+      <c r="AP54" s="3" t="inlineStr"/>
+      <c r="AQ54" s="3" t="inlineStr"/>
+      <c r="AR54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS54" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT54" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 43m</t>
+        </is>
+      </c>
+      <c r="AU54" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW54" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX54" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 4:35 PM</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr"/>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi - 6 Router instal   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>Wifi - 6 Router instal</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379171</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>Sharmila Devi Shakya</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
+          <t>Sharmila Devi Shakya</t>
+        </is>
+      </c>
+      <c r="O55" s="3" t="inlineStr">
+        <is>
+          <t>9841647780</t>
+        </is>
+      </c>
+      <c r="P55" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q55" s="3" t="inlineStr"/>
+      <c r="R55" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 01:30:45 PM</t>
+        </is>
+      </c>
+      <c r="S55" s="3" t="inlineStr"/>
+      <c r="T55" s="3" t="inlineStr"/>
+      <c r="U55" s="3" t="inlineStr">
+        <is>
+          <t>9841647780</t>
+        </is>
+      </c>
+      <c r="V55" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 01:30:24 PM</t>
+        </is>
+      </c>
+      <c r="W55" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 04:34:59 PM</t>
+        </is>
+      </c>
+      <c r="X55" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y55" s="3" t="inlineStr">
+        <is>
+          <t>27.68652</t>
+        </is>
+      </c>
+      <c r="Z55" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA55" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB55" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC55" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD55" s="3" t="inlineStr"/>
+      <c r="AE55" s="3" t="inlineStr">
+        <is>
+          <t>Near NIC asia Bank, Satungal Chowk, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF55" s="3" t="inlineStr">
+        <is>
+          <t>ayodhyastha123@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG55" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH55" s="3" t="inlineStr"/>
+      <c r="AI55" s="3" t="inlineStr">
+        <is>
+          <t>09:04 hour</t>
+        </is>
+      </c>
+      <c r="AJ55" s="3" t="inlineStr"/>
+      <c r="AK55" s="3" t="inlineStr"/>
+      <c r="AL55" s="3" t="inlineStr">
+        <is>
+          <t>Rajnikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM55" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN55" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO55" s="3" t="inlineStr">
+        <is>
+          <t>CDB205A</t>
+        </is>
+      </c>
+      <c r="AP55" s="3" t="inlineStr">
+        <is>
+          <t>85.25113</t>
+        </is>
+      </c>
+      <c r="AQ55" s="3" t="inlineStr"/>
+      <c r="AR55" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi - 6 Router instal   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS55" s="3" t="inlineStr">
+        <is>
+          <t>3d 3h 4m</t>
+        </is>
+      </c>
+      <c r="AT55" s="3" t="inlineStr">
+        <is>
+          <t>3d 3h 4m</t>
+        </is>
+      </c>
+      <c r="AU55" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV55" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi - 6 Router instal   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW55" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX55" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 4:34 PM</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr"/>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi - 6 Router instal   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>Wifi - 6 Router instal</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379171</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>Sharmila Devi Shakya</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
+          <t>Sharmila Devi Shakya</t>
+        </is>
+      </c>
+      <c r="O56" s="3" t="inlineStr">
+        <is>
+          <t>9841647780</t>
+        </is>
+      </c>
+      <c r="P56" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q56" s="3" t="inlineStr"/>
+      <c r="R56" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 01:30:45 PM</t>
+        </is>
+      </c>
+      <c r="S56" s="3" t="inlineStr"/>
+      <c r="T56" s="3" t="inlineStr"/>
+      <c r="U56" s="3" t="inlineStr">
+        <is>
+          <t>9841647780</t>
+        </is>
+      </c>
+      <c r="V56" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 01:30:24 PM</t>
+        </is>
+      </c>
+      <c r="W56" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 04:34:59 PM</t>
+        </is>
+      </c>
+      <c r="X56" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y56" s="3" t="inlineStr">
+        <is>
+          <t>27.68652</t>
+        </is>
+      </c>
+      <c r="Z56" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA56" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB56" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC56" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD56" s="3" t="inlineStr"/>
+      <c r="AE56" s="3" t="inlineStr">
+        <is>
+          <t>Near NIC asia Bank, Satungal Chowk, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF56" s="3" t="inlineStr">
+        <is>
+          <t>ayodhyastha123@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG56" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH56" s="3" t="inlineStr"/>
+      <c r="AI56" s="3" t="inlineStr">
+        <is>
+          <t>09:04 hour</t>
+        </is>
+      </c>
+      <c r="AJ56" s="3" t="inlineStr"/>
+      <c r="AK56" s="3" t="inlineStr"/>
+      <c r="AL56" s="3" t="inlineStr">
+        <is>
+          <t>Rajnikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM56" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN56" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO56" s="3" t="inlineStr">
+        <is>
+          <t>CDB205A</t>
+        </is>
+      </c>
+      <c r="AP56" s="3" t="inlineStr">
+        <is>
+          <t>85.25113</t>
+        </is>
+      </c>
+      <c r="AQ56" s="3" t="inlineStr"/>
+      <c r="AR56" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi - 6 Router instal   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS56" s="3" t="inlineStr">
+        <is>
+          <t>3d 3h 4m</t>
+        </is>
+      </c>
+      <c r="AT56" s="3" t="inlineStr">
+        <is>
+          <t>3d 3h 4m</t>
+        </is>
+      </c>
+      <c r="AU56" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV56" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi - 6 Router instal   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW56" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX56" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Oct_2026.xlsx
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>6</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>71.9%</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>35.1%</t>
         </is>
       </c>
     </row>
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>14.0%</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>38.6%</t>
         </is>
       </c>
     </row>
@@ -854,10 +854,10 @@
         <v>1</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -1054,10 +1054,10 @@
         <v>7</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -1071,7 +1071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX56"/>
+  <dimension ref="A1:AX58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -11305,10 +11305,8 @@
           <t>Rajan Sharma</t>
         </is>
       </c>
-      <c r="O53" s="3" t="inlineStr">
-        <is>
-          <t>9819008606</t>
-        </is>
+      <c r="O53" s="3" t="n">
+        <v>9819008606</v>
       </c>
       <c r="P53" s="3" t="inlineStr">
         <is>
@@ -11398,10 +11396,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN53" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN53" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO53" s="3" t="inlineStr">
         <is>
@@ -11412,7 +11408,7 @@
       <c r="AQ53" s="3" t="inlineStr"/>
       <c r="AR53" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS53" s="3" t="inlineStr">
@@ -11503,20 +11499,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M54" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M54" s="3" t="inlineStr"/>
       <c r="N54" s="3" t="inlineStr">
         <is>
           <t>Brison Maharjan</t>
         </is>
       </c>
-      <c r="O54" s="3" t="inlineStr">
-        <is>
-          <t>9864156296</t>
-        </is>
+      <c r="O54" s="3" t="n">
+        <v>9864156296</v>
       </c>
       <c r="P54" s="3" t="inlineStr">
         <is>
@@ -11606,10 +11596,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN54" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN54" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO54" s="3" t="inlineStr">
         <is>
@@ -11620,7 +11608,7 @@
       <c r="AQ54" s="3" t="inlineStr"/>
       <c r="AR54" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS54" s="3" t="inlineStr">
@@ -11721,10 +11709,8 @@
           <t>Sharmila Devi Shakya</t>
         </is>
       </c>
-      <c r="O55" s="3" t="inlineStr">
-        <is>
-          <t>9841647780</t>
-        </is>
+      <c r="O55" s="3" t="n">
+        <v>9841647780</v>
       </c>
       <c r="P55" s="3" t="inlineStr">
         <is>
@@ -11759,10 +11745,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y55" s="3" t="inlineStr">
-        <is>
-          <t>27.68652</t>
-        </is>
+      <c r="Y55" s="3" t="n">
+        <v>27.68652</v>
       </c>
       <c r="Z55" s="3" t="inlineStr">
         <is>
@@ -11818,25 +11802,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN55" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN55" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO55" s="3" t="inlineStr">
         <is>
           <t>CDB205A</t>
         </is>
       </c>
-      <c r="AP55" s="3" t="inlineStr">
-        <is>
-          <t>85.25113</t>
-        </is>
+      <c r="AP55" s="3" t="n">
+        <v>85.25113</v>
       </c>
       <c r="AQ55" s="3" t="inlineStr"/>
       <c r="AR55" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi - 6 Router instal   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS55" s="3" t="inlineStr">
@@ -11937,10 +11917,8 @@
           <t>Sharmila Devi Shakya</t>
         </is>
       </c>
-      <c r="O56" s="3" t="inlineStr">
-        <is>
-          <t>9841647780</t>
-        </is>
+      <c r="O56" s="3" t="n">
+        <v>9841647780</v>
       </c>
       <c r="P56" s="3" t="inlineStr">
         <is>
@@ -11975,10 +11953,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y56" s="3" t="inlineStr">
-        <is>
-          <t>27.68652</t>
-        </is>
+      <c r="Y56" s="3" t="n">
+        <v>27.68652</v>
       </c>
       <c r="Z56" s="3" t="inlineStr">
         <is>
@@ -12034,53 +12010,377 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN56" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN56" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO56" s="3" t="inlineStr">
         <is>
           <t>CDB205A</t>
         </is>
       </c>
-      <c r="AP56" s="3" t="inlineStr">
-        <is>
-          <t>85.25113</t>
-        </is>
+      <c r="AP56" s="3" t="n">
+        <v>85.25113</v>
       </c>
       <c r="AQ56" s="3" t="inlineStr"/>
       <c r="AR56" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS56" s="3" t="inlineStr">
+        <is>
+          <t>3d 3h 4m</t>
+        </is>
+      </c>
+      <c r="AT56" s="3" t="inlineStr">
+        <is>
+          <t>3d 3h 4m</t>
+        </is>
+      </c>
+      <c r="AU56" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV56" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi - 6 Router instal   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS56" s="3" t="inlineStr">
-        <is>
-          <t>3d 3h 4m</t>
-        </is>
-      </c>
-      <c r="AT56" s="3" t="inlineStr">
-        <is>
-          <t>3d 3h 4m</t>
-        </is>
-      </c>
-      <c r="AU56" s="3" t="inlineStr">
+      <c r="AW56" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX56" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 4:54 PM</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr"/>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr"/>
+      <c r="J57" s="3" t="inlineStr"/>
+      <c r="K57" s="3" t="inlineStr"/>
+      <c r="L57" s="3" t="inlineStr"/>
+      <c r="M57" s="3" t="inlineStr"/>
+      <c r="N57" s="3" t="inlineStr"/>
+      <c r="O57" s="3" t="inlineStr"/>
+      <c r="P57" s="3" t="inlineStr"/>
+      <c r="Q57" s="3" t="inlineStr"/>
+      <c r="R57" s="3" t="inlineStr"/>
+      <c r="S57" s="3" t="inlineStr"/>
+      <c r="T57" s="3" t="inlineStr"/>
+      <c r="U57" s="3" t="inlineStr"/>
+      <c r="V57" s="3" t="inlineStr"/>
+      <c r="W57" s="3" t="inlineStr"/>
+      <c r="X57" s="3" t="inlineStr"/>
+      <c r="Y57" s="3" t="inlineStr"/>
+      <c r="Z57" s="3" t="inlineStr"/>
+      <c r="AA57" s="3" t="inlineStr"/>
+      <c r="AB57" s="3" t="inlineStr"/>
+      <c r="AC57" s="3" t="inlineStr"/>
+      <c r="AD57" s="3" t="inlineStr"/>
+      <c r="AE57" s="3" t="inlineStr"/>
+      <c r="AF57" s="3" t="inlineStr"/>
+      <c r="AG57" s="3" t="inlineStr"/>
+      <c r="AH57" s="3" t="inlineStr"/>
+      <c r="AI57" s="3" t="inlineStr"/>
+      <c r="AJ57" s="3" t="inlineStr"/>
+      <c r="AK57" s="3" t="inlineStr"/>
+      <c r="AL57" s="3" t="inlineStr"/>
+      <c r="AM57" s="3" t="inlineStr"/>
+      <c r="AN57" s="3" t="inlineStr"/>
+      <c r="AO57" s="3" t="inlineStr"/>
+      <c r="AP57" s="3" t="inlineStr"/>
+      <c r="AQ57" s="3" t="inlineStr"/>
+      <c r="AR57" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS57" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT57" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU57" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV57" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW57" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX57" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 4:54 PM</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr"/>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>iptv issue</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379366</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>Paras Mani Ghimire</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
+          <t>Paras Mani Ghimire</t>
+        </is>
+      </c>
+      <c r="O58" s="3" t="inlineStr">
+        <is>
+          <t>9856060074</t>
+        </is>
+      </c>
+      <c r="P58" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q58" s="3" t="inlineStr"/>
+      <c r="R58" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 04:23:16 PM</t>
+        </is>
+      </c>
+      <c r="S58" s="3" t="inlineStr"/>
+      <c r="T58" s="3" t="inlineStr"/>
+      <c r="U58" s="3" t="inlineStr">
+        <is>
+          <t>9856060074</t>
+        </is>
+      </c>
+      <c r="V58" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 04:14:58 PM</t>
+        </is>
+      </c>
+      <c r="W58" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 04:54:44 PM</t>
+        </is>
+      </c>
+      <c r="X58" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y58" s="3" t="inlineStr">
+        <is>
+          <t>27.68426</t>
+        </is>
+      </c>
+      <c r="Z58" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA58" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB58" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC58" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD58" s="3" t="inlineStr"/>
+      <c r="AE58" s="3" t="inlineStr">
+        <is>
+          <t>Matatirtha ward no 6 near Shree Jana Kalyan Secondary School, chandragiri, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF58" s="3" t="inlineStr">
+        <is>
+          <t>parashghimire66@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG58" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH58" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI58" s="3" t="inlineStr">
+        <is>
+          <t>06:40 hour</t>
+        </is>
+      </c>
+      <c r="AJ58" s="3" t="inlineStr"/>
+      <c r="AK58" s="3" t="inlineStr"/>
+      <c r="AL58" s="3" t="inlineStr">
+        <is>
+          <t>Bashu Bhat</t>
+        </is>
+      </c>
+      <c r="AM58" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN58" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO58" s="3" t="inlineStr">
+        <is>
+          <t>CDB346</t>
+        </is>
+      </c>
+      <c r="AP58" s="3" t="inlineStr">
+        <is>
+          <t>85.23489</t>
+        </is>
+      </c>
+      <c r="AQ58" s="3" t="inlineStr"/>
+      <c r="AR58" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS58" s="3" t="inlineStr">
+        <is>
+          <t>3d 31m</t>
+        </is>
+      </c>
+      <c r="AT58" s="3" t="inlineStr">
+        <is>
+          <t>3d 39m</t>
+        </is>
+      </c>
+      <c r="AU58" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="AV56" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi - 6 Router instal   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW56" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="AX56" s="3" t="inlineStr">
+      <c r="AV58" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW58" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX58" s="3" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
         </is>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Oct_2026.xlsx
@@ -1117,7 +1117,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -12233,10 +12233,8 @@
           <t>Paras Mani Ghimire</t>
         </is>
       </c>
-      <c r="O58" s="3" t="inlineStr">
-        <is>
-          <t>9856060074</t>
-        </is>
+      <c r="O58" s="3" t="n">
+        <v>9856060074</v>
       </c>
       <c r="P58" s="3" t="inlineStr">
         <is>
@@ -12271,10 +12269,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y58" s="3" t="inlineStr">
-        <is>
-          <t>27.68426</t>
-        </is>
+      <c r="Y58" s="3" t="n">
+        <v>27.68426</v>
       </c>
       <c r="Z58" s="3" t="inlineStr">
         <is>
@@ -12312,10 +12308,8 @@
           <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
-      <c r="AH58" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH58" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI58" s="3" t="inlineStr">
         <is>
@@ -12334,25 +12328,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN58" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN58" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO58" s="3" t="inlineStr">
         <is>
           <t>CDB346</t>
         </is>
       </c>
-      <c r="AP58" s="3" t="inlineStr">
-        <is>
-          <t>85.23489</t>
-        </is>
+      <c r="AP58" s="3" t="n">
+        <v>85.23488999999999</v>
       </c>
       <c r="AQ58" s="3" t="inlineStr"/>
       <c r="AR58" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS58" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Oct_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>9</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>90.9%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>71.9%</t>
+          <t>72.4%</t>
         </is>
       </c>
     </row>
@@ -688,19 +688,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>76.2%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>36.2%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>13.8%</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>37.9%</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>8</v>
@@ -832,7 +832,7 @@
         <v>3</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
@@ -1045,7 +1045,7 @@
         <v>11</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" s="4" t="n">
         <v>10</v>
@@ -1057,7 +1057,7 @@
         <v>9</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1071,7 +1071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX58"/>
+  <dimension ref="A1:AX59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1117,7 +1117,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -12376,6 +12376,222 @@
         </is>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 5:23 PM</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr"/>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>router upgrade</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>TKT1381454</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>Amir Ratna Shakya</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
+          <t>Amir Ratna Shakya</t>
+        </is>
+      </c>
+      <c r="O59" s="3" t="inlineStr">
+        <is>
+          <t>9841211179</t>
+        </is>
+      </c>
+      <c r="P59" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q59" s="3" t="inlineStr"/>
+      <c r="R59" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 05:23:38 PM</t>
+        </is>
+      </c>
+      <c r="S59" s="3" t="inlineStr"/>
+      <c r="T59" s="3" t="inlineStr"/>
+      <c r="U59" s="3" t="inlineStr">
+        <is>
+          <t>9841211179</t>
+        </is>
+      </c>
+      <c r="V59" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 03:48:26 PM</t>
+        </is>
+      </c>
+      <c r="W59" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 05:23:38 PM</t>
+        </is>
+      </c>
+      <c r="X59" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y59" s="3" t="inlineStr">
+        <is>
+          <t>27.66873</t>
+        </is>
+      </c>
+      <c r="Z59" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA59" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB59" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC59" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD59" s="3" t="inlineStr"/>
+      <c r="AE59" s="3" t="inlineStr">
+        <is>
+          <t>Jyatha Marg, Lalitpur Opposite Of  Ganesh Mandir, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF59" s="3" t="inlineStr">
+        <is>
+          <t>ambhirratna@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG59" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH59" s="3" t="inlineStr"/>
+      <c r="AI59" s="3" t="inlineStr">
+        <is>
+          <t>11:35 hour</t>
+        </is>
+      </c>
+      <c r="AJ59" s="3" t="inlineStr"/>
+      <c r="AK59" s="3" t="inlineStr"/>
+      <c r="AL59" s="3" t="inlineStr">
+        <is>
+          <t>Praktisha Subedi</t>
+        </is>
+      </c>
+      <c r="AM59" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN59" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO59" s="3" t="inlineStr">
+        <is>
+          <t>CDBB42</t>
+        </is>
+      </c>
+      <c r="AP59" s="3" t="inlineStr">
+        <is>
+          <t>85.32638</t>
+        </is>
+      </c>
+      <c r="AQ59" s="3" t="inlineStr"/>
+      <c r="AR59" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS59" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT59" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 35m</t>
+        </is>
+      </c>
+      <c r="AU59" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV59" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW59" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX59" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Oct_2026.xlsx
@@ -1117,7 +1117,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -12443,10 +12443,8 @@
           <t>Amir Ratna Shakya</t>
         </is>
       </c>
-      <c r="O59" s="3" t="inlineStr">
-        <is>
-          <t>9841211179</t>
-        </is>
+      <c r="O59" s="3" t="n">
+        <v>9841211179</v>
       </c>
       <c r="P59" s="3" t="inlineStr">
         <is>
@@ -12481,10 +12479,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y59" s="3" t="inlineStr">
-        <is>
-          <t>27.66873</t>
-        </is>
+      <c r="Y59" s="3" t="n">
+        <v>27.66873</v>
       </c>
       <c r="Z59" s="3" t="inlineStr">
         <is>
@@ -12540,25 +12536,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN59" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN59" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO59" s="3" t="inlineStr">
         <is>
           <t>CDBB42</t>
         </is>
       </c>
-      <c r="AP59" s="3" t="inlineStr">
-        <is>
-          <t>85.32638</t>
-        </is>
+      <c r="AP59" s="3" t="n">
+        <v>85.32638</v>
       </c>
       <c r="AQ59" s="3" t="inlineStr"/>
       <c r="AR59" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS59" s="3" t="inlineStr">
